--- a/Excel/3_5_Enteric_Swine_WIP_v01.xlsx
+++ b/Excel/3_5_Enteric_Swine_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CF1849-44A5-495C-B62D-E9B773852DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8374A056-2AC0-426F-BFF4-EDDC4674F26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="825" windowWidth="37350" windowHeight="19740" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="255" yWindow="390" windowWidth="28545" windowHeight="16950" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,9 +24,6 @@
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId11"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -583,7 +580,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="172">
   <si>
     <t>Home</t>
   </si>
@@ -1142,6 +1139,12 @@
   </si>
   <si>
     <t xml:space="preserve">    Click on a box to go to the corresponding calculation.</t>
+  </si>
+  <si>
+    <t>Livestock type j</t>
+  </si>
+  <si>
+    <t>Average liveweight (kg)</t>
   </si>
 </sst>
 </file>
@@ -2112,7 +2115,7 @@
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2454,6 +2457,9 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="37">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="71">
     <cellStyle name="Alert" xfId="62" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2528,114 +2534,28 @@
     <cellStyle name="Variable type input" xfId="66" xr:uid="{4F3E1D36-2125-457B-B28B-DAF403FCF3B5}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{537B7826-A596-42BB-BEEC-7984101BDA99}"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="91">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4419,20 +4339,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="totalRow" dxfId="98"/>
-      <tableStyleElement type="firstColumn" dxfId="97"/>
-      <tableStyleElement type="firstRowStripe" dxfId="96"/>
-      <tableStyleElement type="secondRowStripe" dxfId="95"/>
+      <tableStyleElement type="wholeTable" dxfId="90"/>
+      <tableStyleElement type="headerRow" dxfId="89"/>
+      <tableStyleElement type="totalRow" dxfId="88"/>
+      <tableStyleElement type="firstColumn" dxfId="87"/>
+      <tableStyleElement type="firstRowStripe" dxfId="86"/>
+      <tableStyleElement type="secondRowStripe" dxfId="85"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="94"/>
-      <tableStyleElement type="headerRow" dxfId="93"/>
-      <tableStyleElement type="totalRow" dxfId="92"/>
-      <tableStyleElement type="firstColumn" dxfId="91"/>
-      <tableStyleElement type="firstRowStripe" dxfId="90"/>
-      <tableStyleElement type="secondRowStripe" dxfId="89"/>
+      <tableStyleElement type="wholeTable" dxfId="84"/>
+      <tableStyleElement type="headerRow" dxfId="83"/>
+      <tableStyleElement type="totalRow" dxfId="82"/>
+      <tableStyleElement type="firstColumn" dxfId="81"/>
+      <tableStyleElement type="firstRowStripe" dxfId="80"/>
+      <tableStyleElement type="secondRowStripe" dxfId="79"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5291,6 +5211,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Total daily production of enteric methane of swine</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -5372,6 +5293,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Total annual methane production from enteric fermentation in swine</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -5498,8 +5420,8 @@
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1397947" cy="321691"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -5637,7 +5559,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -5702,8 +5624,8 @@
       <xdr:rowOff>131108</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2251899" cy="332079"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -5745,6 +5667,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5937,11 +5860,12 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
+              <a:endParaRPr lang="en-AU" sz="1100"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -5997,46 +5921,6 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Overview"/>
-      <sheetName val="Results"/>
-      <sheetName val="Input - Site"/>
-      <sheetName val="Input - Fertiliser"/>
-      <sheetName val="5.1.1.1-2 Inorganic fert N2O"/>
-      <sheetName val="5.1.1.3-4 Inorganic fert CO2"/>
-      <sheetName val="5.2.1.1-2 Organic Fert N2O"/>
-      <sheetName val="5.3.1.1-2 Lime CO2"/>
-      <sheetName val="5.4.1.1-4 Atmos deposition"/>
-      <sheetName val="5.5.1.1-2 Leaching and runoff"/>
-      <sheetName val="Constants - Fertiliser"/>
-      <sheetName val="Constants - Common"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6113,7 +5997,7 @@
     <tableColumn id="1" xr3:uid="{A1AC17BE-6F0C-4EA3-88D1-F15B8A0AA6A1}" name="Class">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_VolatileSolids_Data(), Table_SourceData_Swine_VolatileSolids[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{539845C7-E401-474C-86C5-B676BBD1B040}" name="VSj" dataDxfId="88" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{539845C7-E401-474C-86C5-B676BBD1B040}" name="VSj" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_VolatileSolids_Data(), Table_SourceData_Swine_VolatileSolids[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6144,20 +6028,20 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}" name="Table_SourceData_Swine_FracGASM28" displayName="Table_SourceData_Swine_FracGASM28" ref="D111:F117" totalsRowShown="0" dataDxfId="70" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}" name="Table_SourceData_Swine_FracGASM28" displayName="Table_SourceData_Swine_FracGASM28" ref="D111:F117" totalsRowShown="0" dataDxfId="60" dataCellStyle="Content normal">
   <autoFilter ref="D111:F117" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6DD7EF85-D333-4B03-BD58-78D84BEEC9B4}" name="MMSm" dataDxfId="69" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{6DD7EF85-D333-4B03-BD58-78D84BEEC9B4}" name="MMSm" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F61F4819-1794-4A31-843F-5F15C9F3C95F}" name="EFmT" dataDxfId="68" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F61F4819-1794-4A31-843F-5F15C9F3C95F}" name="EFmT" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B97B38DF-3EA9-445C-BD0D-2CBB24B993D8}" name="NIR reference" dataDxfId="67" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B97B38DF-3EA9-445C-BD0D-2CBB24B993D8}" name="NIR reference" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6192,6 +6076,24 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5546FF29-813A-45A1-A28C-69691DBE2363}" name="Table_SourceData_Swine_Liveweight" displayName="Table_SourceData_Swine_Liveweight" ref="D127:E132" totalsRowShown="0">
+  <autoFilter ref="D127:E132" xr:uid="{5546FF29-813A-45A1-A28C-69691DBE2363}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{39C5E3A8-688C-4C4E-A337-E32C77B7769F}" name="Livestock type j">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{37866161-8EEC-44E3-8B1D-0210A7AFC89C}" name="Average liveweight (kg)" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{E6E3ED7D-B9CD-4192-B821-5B419D60F230}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6213,7 +6115,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{CE2EC9E8-0E91-4093-A370-A0FB47853ED2}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6227,7 +6129,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{32197674-F4EC-40C4-BA61-58B06682F8E5}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6245,7 +6147,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{A03DACCB-4A75-40B0-8551-2B1D21A46594}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6275,7 +6177,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{95132B17-5458-42C3-9E74-261F277F6664}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6299,68 +6201,50 @@
     <tableColumn id="1" xr3:uid="{55DB17EF-0F05-492B-8DF4-50777CFB302F}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C5C83B84-0235-4B48-9882-D789359978A3}" name="MAT" totalsRowDxfId="66" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C5C83B84-0235-4B48-9882-D789359978A3}" name="MAT" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2427DEBF-B9EF-405D-977C-D0B2800FCBB1}" name="MAP" totalsRowDxfId="65" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{2427DEBF-B9EF-405D-977C-D0B2800FCBB1}" name="MAP" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EBA92C07-A154-437D-BDD5-52695464C73C}" name="Frost days per year" totalsRowDxfId="64" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{EBA92C07-A154-437D-BDD5-52695464C73C}" name="Frost days per year" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{99735E8A-3D39-449D-A7C0-CD9B7DAE3957}" name="Elevation" totalsRowDxfId="63" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{99735E8A-3D39-449D-A7C0-CD9B7DAE3957}" name="Elevation" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B79F49BE-04C8-4800-9DCB-948081BBD991}" name="MAP:PET" totalsRowDxfId="62" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{B79F49BE-04C8-4800-9DCB-948081BBD991}" name="MAP:PET" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{223EBFAE-1287-4A0A-AA3E-9342D3BF4364}" name="Min temp" totalsRowDxfId="61" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{223EBFAE-1287-4A0A-AA3E-9342D3BF4364}" name="Min temp" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{351C7274-AFD2-4546-A140-A95A456892E8}" name="Max temp" totalsRowDxfId="60" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{351C7274-AFD2-4546-A140-A95A456892E8}" name="Max temp" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C74C0D42-AEEA-4278-AD59-0334EC505CEC}" name="Min rainfall" totalsRowDxfId="59" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{C74C0D42-AEEA-4278-AD59-0334EC505CEC}" name="Min rainfall" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8B3776A6-D901-494F-A436-67BB3CB20929}" name="Max rainfall" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{8B3776A6-D901-494F-A436-67BB3CB20929}" name="Max rainfall" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{29781557-BEE7-4BC2-8FCF-88051FE8BA04}" name="Min frost days" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{29781557-BEE7-4BC2-8FCF-88051FE8BA04}" name="Min frost days" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{226D5EA0-8392-496D-B07B-0115FF6685C1}" name="Max frost days" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{226D5EA0-8392-496D-B07B-0115FF6685C1}" name="Max frost days" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{97FCC930-F093-4ED4-A18F-679D2FFE3417}" name="Min elevation" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{97FCC930-F093-4ED4-A18F-679D2FFE3417}" name="Min elevation" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{2B589B12-9689-4C72-B4ED-6C287BBF0233}" name="Max elevation" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{2B589B12-9689-4C72-B4ED-6C287BBF0233}" name="Max elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D7A13881-2DB8-4008-8FA2-574069DAD6F6}" name="Min MAP:PET" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{D7A13881-2DB8-4008-8FA2-574069DAD6F6}" name="Min MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2145277F-3B0D-4FA7-97B5-A7338EBFBA01}" name="Max MAP:PET" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2145277F-3B0D-4FA7-97B5-A7338EBFBA01}" name="Max MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{02E9396F-7D92-4EBB-887B-ADD206B4ADDF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
-  <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7C9BA32D-00D8-4C52-9DF7-220AA12DE65F}" name="Climate zone" totalsRowCellStyle="Content bold">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{A81E5122-308B-41E4-B622-AE4C693CCA35}" name="Wet or Dry Zone" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6385,31 +6269,31 @@
     <tableColumn id="1" xr3:uid="{948C8C81-0F25-4404-945E-CD16BE93BFBF}" name="MMS">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="87" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="86" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="85" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="84" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="74" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="83" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="73" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="82" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="72" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="81" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="71" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="80" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="70" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="79" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="69" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6418,6 +6302,24 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{02E9396F-7D92-4EBB-887B-ADD206B4ADDF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+  <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7C9BA32D-00D8-4C52-9DF7-220AA12DE65F}" name="Climate zone" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A81E5122-308B-41E4-B622-AE4C693CCA35}" name="Wet or Dry Zone" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{1A688357-E7C3-4A2A-B4D3-A0F24B08E305}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6443,7 +6345,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{8CCA099A-1815-4C9E-8BE1-EAFCEA3125C3}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6469,7 +6371,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{E1D1277F-7083-467C-A78B-B5A5473D3374}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6487,7 +6389,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C757BE5D-8986-486B-9942-45BFD29D0636}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6505,7 +6407,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{AD5BAE0A-AE6C-4E5D-9102-8C3D108836A9}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6515,7 +6417,7 @@
     <tableColumn id="1" xr3:uid="{BC669E04-ED77-44FE-9D5F-8C8107EB4A98}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A3948F95-F1C4-45B3-81A4-39D322485349}" name="FracWET" dataDxfId="50">
+    <tableColumn id="2" xr3:uid="{A3948F95-F1C4-45B3-81A4-39D322485349}" name="FracWET" dataDxfId="40">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6523,7 +6425,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{77B971EA-407C-45A5-9FFB-F7AA722C8E08}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6553,7 +6455,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{4FD55417-029C-4CE1-94B5-7F7CCA88A962}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6563,7 +6465,7 @@
     <tableColumn id="1" xr3:uid="{5AEF521B-87A4-4DF0-9061-A42BD804FA47}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{413EF7D5-6C1D-48C4-ADE3-C2FBFE9CDBF0}" name="FracWET" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{413EF7D5-6C1D-48C4-ADE3-C2FBFE9CDBF0}" name="FracWET" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6571,7 +6473,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{6D0385FD-EFA3-4C84-B44D-9F37B1305043}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6581,7 +6483,7 @@
     <tableColumn id="1" xr3:uid="{24B3DD1A-762C-4056-B47D-C7F4C3D2140D}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7FA3D3B2-F03B-4A49-B036-1E6713C6C2BA}" name="EFPRP" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7FA3D3B2-F03B-4A49-B036-1E6713C6C2BA}" name="EFPRP" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6589,7 +6491,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{D7CF299F-EB3B-4475-B57E-88E228BFA01A}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6599,7 +6501,7 @@
     <tableColumn id="1" xr3:uid="{891AEBD9-B5D9-477E-A4F8-180604EEEB5F}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{68A7ECE7-9AF7-4FB2-8EBA-0AF2F740F298}" name="Season" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{68A7ECE7-9AF7-4FB2-8EBA-0AF2F740F298}" name="Season" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6607,7 +6509,21 @@
 </table>
 </file>
 
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{42F7033B-606B-4A24-9223-A30737FDC1FE}" name="Table_SourceData_SwineMMS" displayName="Table_SourceData_SwineMMS" ref="D40:E47" totalsRowShown="0">
+  <autoFilter ref="D40:E47" xr:uid="{42F7033B-606B-4A24-9223-A30737FDC1FE}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{EE2AFE6D-8BE2-4C1D-92EA-668A71924A96}" name="MMS"/>
+    <tableColumn id="2" xr3:uid="{58174C83-0911-44A2-9C27-90139AD99654}" name="Symbol and MMS"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{55A68CD2-471B-4B4F-9D5E-65C39267BD6F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6631,49 +6547,49 @@
     <tableColumn id="1" xr3:uid="{36D78F8A-058B-42CA-B726-7AEBBCA6C28C}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1091063A-29C3-4F2A-BFEF-BD86006AD144}" name="MAT (ºC)" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1091063A-29C3-4F2A-BFEF-BD86006AD144}" name="MAT (ºC)" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D8D6B89D-F8F7-4100-9AC6-7433F92DE90E}" name="Anaerobic lagoon" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D8D6B89D-F8F7-4100-9AC6-7433F92DE90E}" name="Anaerobic lagoon" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5AD0EE1F-0F8D-4B1E-BC41-D905561F457C}" name="Digester / covered lagoons" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5AD0EE1F-0F8D-4B1E-BC41-D905561F457C}" name="Digester / covered lagoons" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{70A47EB3-89E9-49EA-A584-4FFFF617FFFE}" name="Liquid systems" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{70A47EB3-89E9-49EA-A584-4FFFF617FFFE}" name="Liquid systems" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6379D57A-CF72-4017-8026-7368D62E7C6E}" name="Daily spread" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{6379D57A-CF72-4017-8026-7368D62E7C6E}" name="Daily spread" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A8CAA5F5-A9E2-490C-8E9E-F98FEC2B85B7}" name="Composting (passive windrow)" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{A8CAA5F5-A9E2-490C-8E9E-F98FEC2B85B7}" name="Composting (passive windrow)" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2932A796-896E-4749-8473-D4D99CB5A8DA}" name="Solid storage" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{2932A796-896E-4749-8473-D4D99CB5A8DA}" name="Solid storage" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B15FC1CD-D6D4-48C6-BB02-0784024F60E1}" name="Pit storage" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{B15FC1CD-D6D4-48C6-BB02-0784024F60E1}" name="Pit storage" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BEBE432B-3D78-4900-9DC3-1FD9ACCBB17C}" name="Deep litter" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{BEBE432B-3D78-4900-9DC3-1FD9ACCBB17C}" name="Deep litter" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A81D0680-FD86-4172-B5F0-E4CCA7F0900F}" name="Poultry manure with bedding" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{A81D0680-FD86-4172-B5F0-E4CCA7F0900F}" name="Poultry manure with bedding" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BE403667-5932-4CF5-8344-621BAA196406}" name="Poultry manure without bedding" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{BE403667-5932-4CF5-8344-621BAA196406}" name="Poultry manure without bedding" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D72C37E3-C784-49F8-9FFA-148700905D66}" name="Direct processing" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{D72C37E3-C784-49F8-9FFA-148700905D66}" name="Direct processing" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FECAD450-29C4-40CA-9D51-7672268D9D32}" name="Direct application" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{FECAD450-29C4-40CA-9D51-7672268D9D32}" name="Direct application" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3BCC1851-11A9-41A2-B4BC-E7AFBD1EAA84}" name="Pasture range and paddock" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{3BCC1851-11A9-41A2-B4BC-E7AFBD1EAA84}" name="Pasture range and paddock" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{69CC47FE-434C-431F-B727-358EA13CFB6F}" name="MAT raw" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{69CC47FE-434C-431F-B727-358EA13CFB6F}" name="MAT raw" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6681,21 +6597,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{42F7033B-606B-4A24-9223-A30737FDC1FE}" name="Table_SourceData_SwineMMS" displayName="Table_SourceData_SwineMMS" ref="D40:E47" totalsRowShown="0">
-  <autoFilter ref="D40:E47" xr:uid="{42F7033B-606B-4A24-9223-A30737FDC1FE}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EE2AFE6D-8BE2-4C1D-92EA-668A71924A96}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{58174C83-0911-44A2-9C27-90139AD99654}" name="Symbol and MMS"/>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
   <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6774,7 +6676,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}" name="Table_SourceData_Swine_NitrogenInWaste" displayName="Table_SourceData_Swine_NitrogenInWaste" ref="D89:G93" totalsRowShown="0" dataDxfId="78" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}" name="Table_SourceData_Swine_NitrogenInWaste" displayName="Table_SourceData_Swine_NitrogenInWaste" ref="D89:G93" totalsRowShown="0" dataDxfId="68" dataCellStyle="Content normal">
   <autoFilter ref="D89:G93" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6782,16 +6684,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1C4094D2-E798-4EA4-8FBC-50FBA0E527D4}" name="Class" dataDxfId="77" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{1C4094D2-E798-4EA4-8FBC-50FBA0E527D4}" name="Class" dataDxfId="67" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BD1910A-3F15-4C45-9A95-D2ADDB197E82}" name="NWj" dataDxfId="76" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BD1910A-3F15-4C45-9A95-D2ADDB197E82}" name="NWj" dataDxfId="66" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06D949C0-1431-4E8B-9FED-E08C8D4D7E61}" name="NWj Daily" dataDxfId="75" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{06D949C0-1431-4E8B-9FED-E08C8D4D7E61}" name="NWj Daily" dataDxfId="65" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5C9C6F5B-830D-4A53-BEF6-FDE389E9F8CC}" name="Class name" dataDxfId="74" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5C9C6F5B-830D-4A53-BEF6-FDE389E9F8CC}" name="Class name" dataDxfId="64" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6800,16 +6702,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}" name="Table_SourceData_Swine_FeedIntake" displayName="Table_SourceData_Swine_FeedIntake" ref="D78:E82" totalsRowShown="0" dataDxfId="73" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}" name="Table_SourceData_Swine_FeedIntake" displayName="Table_SourceData_Swine_FeedIntake" ref="D78:E82" totalsRowShown="0" dataDxfId="63" dataCellStyle="Content normal">
   <autoFilter ref="D78:E82" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CAC8EB28-568F-4E9F-8E36-EBDFF74A58D3}" name="Class" dataDxfId="72" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{CAC8EB28-568F-4E9F-8E36-EBDFF74A58D3}" name="Class" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_FeedIntake_Data(), Table_SourceData_Swine_FeedIntake[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2CE09F11-701B-40A5-9E2D-B745C440FD8B}" name="Ij" dataDxfId="71" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2CE09F11-701B-40A5-9E2D-B745C440FD8B}" name="Ij" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_FeedIntake_Data(), Table_SourceData_Swine_FeedIntake[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9803,107 +9705,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E205:G205">
-    <cfRule type="cellIs" dxfId="31" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F40:F41">
-    <cfRule type="cellIs" dxfId="30" priority="69" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="69" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="cellIs" dxfId="29" priority="68" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="68" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="cellIs" dxfId="28" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121:F122">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133:F134">
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F145:F146">
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F157:F158">
-    <cfRule type="cellIs" dxfId="24" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F245:F246">
-    <cfRule type="cellIs" dxfId="23" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="22" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="21" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F279:F280">
-    <cfRule type="cellIs" dxfId="20" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="19" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="18" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29:I34">
-    <cfRule type="cellIs" dxfId="17" priority="55" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="55" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I55:I59">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:I66">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I70:I73">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I77:I80">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I88">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:L43 I48:I51 J101 I119 I199 I205">
-    <cfRule type="cellIs" dxfId="0" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12512,69 +12414,123 @@
       <c r="M124" s="1"/>
     </row>
     <row r="125" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D125" s="6" t="str" cm="1">
+        <f t="array" ref="D125">SourceData_Swine.SourceData_Swine_AverageLiveweight_Title()</f>
+        <v>Swine - Average liveweight (inventory defaults) (kg) (Wco)</v>
+      </c>
       <c r="M125" s="1"/>
       <c r="V125" s="1"/>
     </row>
     <row r="126" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D126" s="5" t="str" cm="1">
+        <f t="array" ref="D126">SourceData_Swine.SourceData_Swine_AverageLiveweight_Source()</f>
+        <v>VEERG 2026: Table A.1.6.5: Swine - Average liveweight (inventory defaults) (kg) (Wco)</v>
+      </c>
       <c r="M126" s="1"/>
       <c r="V126" s="1"/>
     </row>
     <row r="127" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D127" s="126" t="s">
+        <v>170</v>
+      </c>
+      <c r="E127" s="126" t="s">
+        <v>171</v>
+      </c>
       <c r="M127" s="1"/>
       <c r="V127" s="1"/>
     </row>
     <row r="128" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D128" s="126" t="str" cm="1">
+        <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>Sows</v>
+      </c>
+      <c r="E128" s="126" cm="1">
+        <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>188</v>
+      </c>
       <c r="M128" s="1"/>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D129" s="1" t="str" cm="1">
+        <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>Boars</v>
+      </c>
+      <c r="E129" s="34" cm="1">
+        <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>206</v>
+      </c>
       <c r="M129" s="1"/>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D130" s="1" t="str" cm="1">
+        <f t="array" ref="D130">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>Gilts</v>
+      </c>
+      <c r="E130" s="34" cm="1">
+        <f t="array" ref="E130">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>125</v>
+      </c>
       <c r="M130" s="1"/>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D131" s="1" t="str" cm="1">
+        <f t="array" ref="D131">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>Slaughter pigs</v>
+      </c>
+      <c r="E131" s="34" cm="1">
+        <f t="array" ref="E131">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>39</v>
+      </c>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="1" t="str" cm="1">
+        <f t="array" ref="D132">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>Slaughter pigs at turnoff</v>
+      </c>
+      <c r="E132" s="34" cm="1">
+        <f t="array" ref="E132">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
+        <v>97</v>
+      </c>
       <c r="M132" s="1"/>
     </row>
-    <row r="133" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M134" s="1"/>
     </row>
-    <row r="135" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M135" s="1"/>
     </row>
-    <row r="136" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M137" s="1"/>
     </row>
-    <row r="138" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M138" s="1"/>
     </row>
-    <row r="139" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M140" s="1"/>
     </row>
-    <row r="141" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M143" s="1"/>
     </row>
-    <row r="144" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M144" s="1"/>
     </row>
     <row r="145" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13503,7 +13459,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="13">
+  <tableParts count="14">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -13517,6 +13473,7 @@
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17942,14 +17899,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABTAHcAaQBuAGUAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXABuAFYAUwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAKABWAFMAagApACAALQAgADIAMAAyADAAIAB0AG8AIAAyADAAMgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE8AbgBsAHkAIAB1AHMAZQBzACAAZABhAHQAYQAgAGYAbwByACAAMgAwADIAMAAtADIAMAAyADQALgAgAFUAcwBlACAAJwBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAJwAgAGQAYQB0AGEAIABmAG8AcgAgACcATwB0AGgAZQByACAAagA9ADQAJwAgAGMAbABhAHMAcwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABhAHMAcwBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMAAuADQAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsACAAMAAuADQANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGkAbAB0AHMAXAAiACwAIAAwAC4ANQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzAFwAIgAsACAAMAAuADMAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAFwAbgBJAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAEYAZQBlAGQAIABpAG4AdABhAGsAZQAgAC0AIABpAG4AZwBlAHMAdABlAGQAIABhAHMAIABmAGUAZAAgACAAKABJAGoAKQAgAC0AIAAyADAAMgAwACAAdABvACAAMgAwADIANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABPAG4AbAB5ACAAdQBzAGUAcwAgAGQAYQB0AGEAIABmAG8AcgAgADIAMAAyADAALQAyADAAMgA0AC4AIABVAHMAZQAgACcAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzACcAIABkAGEAdABhACAAZgBvAHIAIAAnAE8AdABoAGUAcgAgAGoAPQA0ACcAIABjAGwAYQBzAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAEkAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMgAuADYAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADIALgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMgAuADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAcwBcACIALAAgADEALgA3ADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBcAG4ATgBXAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB3AGEAcwB0AGUAIAAoAE4AVwBqACkAIAAtACAAMgAwADIAMAAgAHQAbwAgADIAMAAyADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATwBuAGwAeQAgAHUAcwBlAHMAIABkAGEAdABhACAAZgBvAHIAIAAyADAAMgAwAC0AMgAwADIANAAuACAAVQBzAGUAIAAnAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwAnACAAZABhAHQAYQAgAGYAbwByACAAJwBPAHQAaABlAHIAIABqAD0ANAAnACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAE4AVwBqACAAZABhAGkAbAB5ACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAHAAcgBvAHYAaQBkAGUAIABkAGEAaQBsAHkAIAB2AGEAbAB1AGUAIABmAG8AcgAgAE8AdABoAGUAcgBzACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAEMAbABhAHMAcwAgAG4AYQBtAGUAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAE4AVwBqAFwAIgAsACAAXAAiAE4AVwBqACAAZABhAGkAbAB5AFwAIgAsACAAXAAiAEMAbABhAHMAcwAgAG4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADAALgAwADQANgAsACAAMAAuADAANAA2ACwAIABcACIAQgBvAGEAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADAALgAwADQAOQAsACAAMAAuADAANAA5ACwAIABcACIAUwBvAHcAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMAAuADAANAA2ACwAIAAwAC4AMAA0ADYALAAgAFwAIgBHAGkAbAB0AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzACAAKABrAGcALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAIgAsACAAMQAxAC4ANAAsACAAMAAuADAAMwAxADIALAAgAFwAIgBPAHQAaABlAHIAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUAFwAbgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMgA6ACAAUwB3AGkAbgBlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcATgApACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByACAAKABEAHIAeQAgAGwAbwB0ACkAXAAiACwAIAAwAC4AMwAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADEAMgA1ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALgA1ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AGUAcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAEYAcgBhAGMARwBBAFMATQBtAFQAXABuAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABFAEYAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMwA6ACAAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABrAGcATgAyAE8ALQBOAC8AawBnAE4AKQAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAbQBcACIALAAgAFwAIgBFAEYAbQBUAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdQB0AGQAbwBvAHIAIAAoAEQAcgB5ACAAbABvAHQAKQBcACIALAAgADAALgAwADIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADEALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABvAGMAawBwAGkAbABlACAAKABTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMAAyACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQgAwAFwAbgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIABtAGUAdABoAGEAbgBlACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAoADIAMAAxADkAKQAsACAAQwBoAGEAcAB0AGUAcgAgADEAMAAgAFsANABdAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgA2AC4ANAA6ACAAUwB3AGkAbgBlACAALQAgAE0AQwBGAHMAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAAtACAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAEEAQwBUACwAIABzAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAxADAALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcAOAAsACAAMAAuADcAOAAsACAAMAAuADcANQAsACAAMAAuADcAMAAsACAAMAAuADcANAAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAZQByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVwBjAG8AXABuAGsAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIAAtACAAQQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGkAbgB2AGUAbgB0AG8AcgB5ACAAZABlAGYAYQB1AGwAdABzACkAIAAoAGsAZwApACAAKABXAGMAbwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADUAOgAgAFMAdwBpAG4AZQAgAC0AIABBAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAaQBuAHYAZQBuAHQAbwByAHkAIABkAGUAZgBhAHUAbAB0AHMAKQAgACgAawBnACkAIAAoAFcAYwBvACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHcAcwBcACIALAAgADEAOAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADIAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAaQBsAHQAcwBcACIALAAgADEAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwBcACIALAAgADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAIABhAHQAIAB0AHUAcgBuAG8AZgBmAFwAIgAsACAAOQA3AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBcAG4ANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG4AdgBlAG4AdABpAG8AbgBhAGwAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByAC8AZgByAGUAZQAgAHIAYQBuAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBcAG4ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGUAeAB0ACAAcgBlAGYAZQByAHMAIAB0AG8AIAAnAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAJwAgAE0ATQBTACwAIABiAHUAdAAgAGUAcQB1AGEAdABpAG8AbgAgAHIAZQBmAGUAcgBzACAAdABvACAAJwBkAHIAeQBsAG8AdAAnACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAFwAbgBGAFwAbgBNAEoALwBrAGcAIABDAEgANABcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcAIABDAEgANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADUALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA1ADUALgAyADIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqACAAPQAgAHQAaABlACAAYQB2AGUAcgBhAGcAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAHkAcwAgAG8AbgAgAGYAYQByAG0AIABmAG8AcgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIAAoAE4AXwBqACAAKgAgAE0AXwBqACAAKgAgAEQAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4ANQAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAdABoAGUAIABhAHYAZQByAGEAZwBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAeQBzACAAbwBuACAAZgBhAHIAbQAgAGYAbwByACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABvAGYAIABzAHcAaQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcAG4ASQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAZgBlAGUAZAAgAGkAbgBnAGUAcwB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBGACAAPQAgAG0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoAE0ASgAvAGsAZwAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAARgAsAFwAbgAgACAAIAAgACgASQBfAGoAIAAqACAAMQA4AC4ANgAgACoAIAAwAC4AMAAwADcAKQAgAC8AIABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABmAGUAZQBkACAAaQBuAGcAZQBzAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADgALgA2AFwAIgAsACAAXAAiAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAKABHAEUAKQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkAFwAIgAsACAAXAAiAE0ASgAgAEcARQAvAGsAZwAgAGYAZQBlAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAC4AMAAwADcAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAARwBFACAAaQBuAHQAYQBrAGUAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAG0AZQB0AGgAYQBuAGUAIABiAHkAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBcACIALAAgAFwAIgBtAGUAZwBhAGoAbwB1AGwAZQBzACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAE0ASgAvAGsAZwAgAEMASAA0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAAFCAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlACAAOgAgAGQAYQB5AHMAXABuAE0AbQBqACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAagAsACAATQBtAGoALAAgAE4AagAsAFwAbgAgACAAIAAgAEQAagAgACoAIABNAG0AagAgACoAIABOAGoAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGoAXAAiACwAXAAiAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbQBqAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXABuAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAbgBNAG0AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcAG4ATQBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBsAGEAcwBzACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUACwAXABuACAAIAAgACAAUwBVAE0AKABNAGoAbQBUACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUADEALAAgAE0AagBtAFQAMgAsAFwAbgAgACAAIAAgACAAUwBVAE0AKABNAGoAbQBUADEALAAgAE0AagBtAFQAMgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBtAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBtAGoAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAbQBUAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AagBtAFQAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgAMwApACAAYQBuAGQAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAE0AagBtACAAaQBuAHQAbwAgAE0AagBtAFQAMQAgAGEAbgBkACAATQBqAG0AVAAyACAAZgBvAHIAIABzAHQAYQBnAGUAIAAxACAAYQBuAGQAIAAyACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AaQBqAG0AVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBGAFYAUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBqACwAIABGAFYAUwBqAG0AVAAxACwAIABNAEMARgBpAG0ALAAgAEIATwAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAagAgACoAIABGAFYAUwBqAG0AVAAxACAAKgAgAE0AQwBGAGkAbQAgACoAIABCAE8AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBWAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADEAIAAoADQAKQAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAFYAUwBqAG0AVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAHAAcgBpAG8AcgAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAZQBwAGEAcgBhAHQAaQBvAG4AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATQBNAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAcAByAGkAbwByACAAdABvACAAcwBvAGwAaQBkACAAcwBlAHAAYQByAGEAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAbQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXABuAEYAVgBTAGoAbQA0AFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0ANABUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBNAFMAagBtADEANwA5AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAE0ATQBTACAAMQAsACAANwAsACAAYQBuAGQAIAA5ACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AUwBTAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAIABNAE0AUwBqAG0AMQA3ADkAVAAxACwAIABTAFMAbQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIAAoAE0ATQBTAGoAbQAxADcAOQBUADEAIAAqACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAATQBNAFMAagBtAFQAMQBfADMALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAUwBTAGoAbQBUADEAXwAyACwAIABTAFMAagBtAFQAMQBfADMALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAUwBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMQAgACoAIABTAFMAagBtAFQAMQBfADEAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMwAgACoAIABTAFMAagBtAFQAMQBfADMAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwA1ACAAKgAgAFMAUwBqAG0AVAAxAF8ANQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQAxACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA3ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0ANwAsAFQAPQAxAH0AKQArACgATQBNAFMAXwB7AGoALABtAD0AOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADkALABUAD0AMQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQA0AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQAxADcAOQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBTAG0AXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAGUAcQB1AGEAdABpAG8AbgAgAGYAbwByACAATQBNAFMAbQA9ADEALAA3ACwAOQAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABpAHQAZQBtAHMAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcACIAKQA7AFwAbgAgACAAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABlAGEAYwBoACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0AaQBqAG0AVAAyAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAVABqAG0AVAAyACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAGkAIAA9ACAAcwB0AGEAdABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAAQgBPACwAIABNAE0AUwBqAG0AVAAyACwAIABNAEMARgBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAVgBTAFQAagBtAFQAMgApACwAIABWAFMAVABqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBNAFMAagBtAFQAMgApACwAIABNAE0AUwBqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAgACoAIABCAE8AIAAqACAATQBNAFMAagBtAFQAMgAgACoAIABNAEMARgBpAG0AIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAXAAiACwAXAAiAE0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgCwAEMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4AVgBTAFQAaQBqAG0AVAAyAFwAbgBrAGcAIABWAFMAXABuAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARgBWAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBWAFMATABtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAFYAUwBMAG0AVAAxACwAXABuACAAIAAgACAAVgBTAGoAIAAqACAARgBWAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAVgBTAEwAbQBUADEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANAApACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMATABtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AagBtACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEUARgBfAGoAbQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAyACkAKAA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAbQBcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AVAAxAFwAbgBrAGcAIABOAFwAbgBNAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBqAG0ALABUAD0AMQB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4AKQBcAG4ARgBOAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAARgBOAF8AagBtAFQAMQAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAARgBOAF8AagBtAFQAMQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AGoAbQAsAFQAPQAxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBfAGoAXAAiACwAIABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AXwBqAG0AVAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAzACkAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAKQBcAG4ARgBOAF8AagBtAFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMATgBfAHsAbQB9ACkAXABuAE0ATQBTAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4AUwBOAF8AbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACwAIABTAE4AXwBtACwAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABTAE4AXwBtACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBOAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAE4AXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBOAF8AagBtADQAVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAbgBNAE0AUwBfAGoAbQA0AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcAG4ATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAGwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADEALAA3ACwAOQApAFwAbgBTAE4AXwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALAAgAE0ATQBTAF8AagBtADEANwA5AFQAMQAsACAAUwBOAF8AbQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAKgAgAFMATgBfAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxAF8AMQAsACAATQBNAFMAagBtAFQAMQBfADIALAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIABNAE0AUwBqAG0AVAAxAF8ANAAsACAATQBNAFMAagBtAFQAMQBfADUALABcAG4AIAAgACAAIABTAFMAagBtAFQAMQBfADEALAAgAFMAUwBqAG0AVAAxAF8AMgAsACAAUwBTAGoAbQBUADEAXwAzACwAIABTAFMAagBtAFQAMQBfADQALAAgAFMAUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAagBtAFQAMQBfADEAIAAqACAAUwBTAGoAbQBUADEAXwAxACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIAAoAE0ATQBTAGoAbQBUADEAXwAzACAAKgAgAFMAUwBqAG0AVAAxAF8AMwApACAAKwAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8ANQAgACoAIABTAFMAagBtAFQAMQBfADUAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AewBqAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADEALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADcALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA3ACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AOQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQA0AFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQAxADcAOQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAbABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzACAAKABtAD0AMQAsADcALAA5ACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBOAF8AbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABTAHAAbABpAHQAIABlAHEAdQBhAHQAaQBvAG4AIABmAG8AcgAgAE0ATQBTAG0APQAxACwANwAsADkAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAaQB0AGUAbQBzACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAFcAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAAoAGgAZQBhAGQAKQBcAG4ATgBXAF8AagAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAHIAbwBkAHUAYwBlAGQAIABpAG4AIABzAHcAaQBuAGUAIABtAGEAbgB1AHIAZQAgAGEAbgBkACAAdwBhAHMAdABlACAAZgBlAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcAAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4AVwBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBXAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBXAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVwBfAGoAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcAByAG8AZAB1AGMAZQBkACAAaQBuACAAcwB3AGkAbgBlACAAbQBhAG4AdQByAGUAIABhAG4AZAAgAHcAYQBzAHQAZQAgAGYAZQBlAGQAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAcwB3AGkAbgBlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAsACAATQBNAFMAXwBqAG0AVAAyACwAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAgACoAIABNAE0AUwBfAGoAbQBUADIAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQAsAFQAPQAyAH0APQBOAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE4AVABfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE4AVABfAHsAagBtACwAVAA9ADIAfQA9AE0ATgBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQAsAFQAPQAxAH0ALQBFAEYAXwB7AG0ALABUAD0AMQB9ACkAXABuAE0ATgBfAGoAbQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ARQBGAF8AbQBUADEAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMQAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAxACwAIABFAEYAXwBtAFQAMQAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBtAFQAMQAgAC0AIABFAEYAXwBtAFQAMQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AewBqAG0ALABUAD0AMgB9AD0ATQBOAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtACwAVAA9ADEAfQAtAEUARgBfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAxAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGEAdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADUAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABEAGUAcABvAHMAaQB0AGkAbwBuACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXABuAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAbgBFAF8ATgAyAE8ATQBNAFMAYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAEEAVABNAE8AUwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAE0ATQBTAGEAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGEAZAB9AD0ATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AQQBUAE0ATwBTAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA1ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXABuAFQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwBcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBHAEEAUwBNAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADIAKQAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4ANwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEwAZQBhAGMAaABpAG4AZwAgAEEAbgBkACAAUgB1AG4AbwBmAGYAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAFwAbgBBAG4AbgB1AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZQBhAGMAaAAgAE0ATQBTAFwAbgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAE4ATABlAGEAYwBoAF8AewBqAG0APQA1AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEQAdQBlACAAdABvACAAcwB0AHIAaQBjAHQAIABlAG4AdgBpAHIAbwBuAG0AZQBuAHQAYQBsACAAYwBvAG4AdAByAG8AbABzACwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGEAcgBlACAAZQBzAHQAaQBtAGEAdABlAGQAIABvAG4AbAB5ACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABtAD0ANQApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGUAYQBjAGgAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAXABuAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBXAEUAVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMAVwBFAFQALAAgAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACwAXABuACAAIAAgACAATQBOAF8AagBtADUAVAAxACAAKgAgAEYAcgBhAGMAVwBFAFQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIALAAgAEUARgBfAG0AVAAyACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAsACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACkAIAAtACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA3ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABwAGkAZwBnAGUAcgB5ACAAYgBvAHUAbgBkAGEAcgB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcABpAGcAZwBlAHIAeQAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAsACAARQBGAF8AbQBUADIALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACwAIABNAE4ATABlAGEAYwBoAF8AagBtADUALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAKQAgAC0AIABNAE4ATABlAGEAYwBoAF8AagBtADUAKQAgACoAIAAoADEAIAAtACAAUABGACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABGAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18148,7 +18098,14 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABTAHcAaQBuAGUAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXABuAFYAUwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAKABWAFMAagApACAALQAgADIAMAAyADAAIAB0AG8AIAAyADAAMgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE8AbgBsAHkAIAB1AHMAZQBzACAAZABhAHQAYQAgAGYAbwByACAAMgAwADIAMAAtADIAMAAyADQALgAgAFUAcwBlACAAJwBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAJwAgAGQAYQB0AGEAIABmAG8AcgAgACcATwB0AGgAZQByACAAagA9ADQAJwAgAGMAbABhAHMAcwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABhAHMAcwBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMAAuADQAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsACAAMAAuADQANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGkAbAB0AHMAXAAiACwAIAAwAC4ANQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzAFwAIgAsACAAMAAuADMAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAFwAbgBJAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAEYAZQBlAGQAIABpAG4AdABhAGsAZQAgAC0AIABpAG4AZwBlAHMAdABlAGQAIABhAHMAIABmAGUAZAAgACAAKABJAGoAKQAgAC0AIAAyADAAMgAwACAAdABvACAAMgAwADIANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABPAG4AbAB5ACAAdQBzAGUAcwAgAGQAYQB0AGEAIABmAG8AcgAgADIAMAAyADAALQAyADAAMgA0AC4AIABVAHMAZQAgACcAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzACcAIABkAGEAdABhACAAZgBvAHIAIAAnAE8AdABoAGUAcgAgAGoAPQA0ACcAIABjAGwAYQBzAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAEkAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMgAuADYAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADIALgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMgAuADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAcwBcACIALAAgADEALgA3ADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBcAG4ATgBXAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB3AGEAcwB0AGUAIAAoAE4AVwBqACkAIAAtACAAMgAwADIAMAAgAHQAbwAgADIAMAAyADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATwBuAGwAeQAgAHUAcwBlAHMAIABkAGEAdABhACAAZgBvAHIAIAAyADAAMgAwAC0AMgAwADIANAAuACAAVQBzAGUAIAAnAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwAnACAAZABhAHQAYQAgAGYAbwByACAAJwBPAHQAaABlAHIAIABqAD0ANAAnACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAE4AVwBqACAAZABhAGkAbAB5ACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAHAAcgBvAHYAaQBkAGUAIABkAGEAaQBsAHkAIAB2AGEAbAB1AGUAIABmAG8AcgAgAE8AdABoAGUAcgBzACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAEMAbABhAHMAcwAgAG4AYQBtAGUAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAE4AVwBqAFwAIgAsACAAXAAiAE4AVwBqACAAZABhAGkAbAB5AFwAIgAsACAAXAAiAEMAbABhAHMAcwAgAG4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADAALgAwADQANgAsACAAMAAuADAANAA2ACwAIABcACIAQgBvAGEAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADAALgAwADQAOQAsACAAMAAuADAANAA5ACwAIABcACIAUwBvAHcAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMAAuADAANAA2ACwAIAAwAC4AMAA0ADYALAAgAFwAIgBHAGkAbAB0AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzACAAKABrAGcALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAIgAsACAAMQAxAC4ANAAsACAAMAAuADAAMwAxADIALAAgAFwAIgBPAHQAaABlAHIAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUAFwAbgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMgA6ACAAUwB3AGkAbgBlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcATgApACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByACAAKABEAHIAeQAgAGwAbwB0ACkAXAAiACwAIAAwAC4AMwAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADEAMgA1ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALgA1ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AGUAcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAEYAcgBhAGMARwBBAFMATQBtAFQAXABuAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABFAEYAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMwA6ACAAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABrAGcATgAyAE8ALQBOAC8AawBnAE4AKQAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAbQBcACIALAAgAFwAIgBFAEYAbQBUAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdQB0AGQAbwBvAHIAIAAoAEQAcgB5ACAAbABvAHQAKQBcACIALAAgADAALgAwADIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADEALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABvAGMAawBwAGkAbABlACAAKABTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMAAyACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQgAwAFwAbgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIABtAGUAdABoAGEAbgBlACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAoADIAMAAxADkAKQAsACAAQwBoAGEAcAB0AGUAcgAgADEAMAAgAFsANABdAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgA2AC4ANAA6ACAAUwB3AGkAbgBlACAALQAgAE0AQwBGAHMAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAAtACAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAEEAQwBUACwAIABzAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAxADAALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcAOAAsACAAMAAuADcAOAAsACAAMAAuADcANQAsACAAMAAuADcAMAAsACAAMAAuADcANAAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAZQByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVwBjAG8AXABuAGsAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIAAtACAAQQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGkAbgB2AGUAbgB0AG8AcgB5ACAAZABlAGYAYQB1AGwAdABzACkAIAAoAGsAZwApACAAKABXAGMAbwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADUAOgAgAFMAdwBpAG4AZQAgAC0AIABBAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAaQBuAHYAZQBuAHQAbwByAHkAIABkAGUAZgBhAHUAbAB0AHMAKQAgACgAawBnACkAIAAoAFcAYwBvACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHcAcwBcACIALAAgADEAOAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADIAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAaQBsAHQAcwBcACIALAAgADEAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwBcACIALAAgADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAIABhAHQAIAB0AHUAcgBuAG8AZgBmAFwAIgAsACAAOQA3AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBcAG4ANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG4AdgBlAG4AdABpAG8AbgBhAGwAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByAC8AZgByAGUAZQAgAHIAYQBuAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBcAG4ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGUAeAB0ACAAcgBlAGYAZQByAHMAIAB0AG8AIAAnAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAJwAgAE0ATQBTACwAIABiAHUAdAAgAGUAcQB1AGEAdABpAG8AbgAgAHIAZQBmAGUAcgBzACAAdABvACAAJwBkAHIAeQBsAG8AdAAnACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAFwAbgBGAFwAbgBNAEoALwBrAGcAIABDAEgANABcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcAIABDAEgANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADUALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA1ADUALgAyADIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqACAAPQAgAHQAaABlACAAYQB2AGUAcgBhAGcAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAHkAcwAgAG8AbgAgAGYAYQByAG0AIABmAG8AcgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIAAoAE4AXwBqACAAKgAgAE0AXwBqACAAKgAgAEQAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4ANQAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAdABoAGUAIABhAHYAZQByAGEAZwBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAeQBzACAAbwBuACAAZgBhAHIAbQAgAGYAbwByACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABvAGYAIABzAHcAaQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcAG4ASQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAZgBlAGUAZAAgAGkAbgBnAGUAcwB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBGACAAPQAgAG0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoAE0ASgAvAGsAZwAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAARgAsAFwAbgAgACAAIAAgACgASQBfAGoAIAAqACAAMQA4AC4ANgAgACoAIAAwAC4AMAAwADcAKQAgAC8AIABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABmAGUAZQBkACAAaQBuAGcAZQBzAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADgALgA2AFwAIgAsACAAXAAiAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAKABHAEUAKQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkAFwAIgAsACAAXAAiAE0ASgAgAEcARQAvAGsAZwAgAGYAZQBlAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAC4AMAAwADcAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAARwBFACAAaQBuAHQAYQBrAGUAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAG0AZQB0AGgAYQBuAGUAIABiAHkAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBcACIALAAgAFwAIgBtAGUAZwBhAGoAbwB1AGwAZQBzACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAE0ASgAvAGsAZwAgAEMASAA0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAAFCAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlACAAOgAgAGQAYQB5AHMAXABuAE0AbQBqACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAagAsACAATQBtAGoALAAgAE4AagAsAFwAbgAgACAAIAAgAEQAagAgACoAIABNAG0AagAgACoAIABOAGoAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGoAXAAiACwAXAAiAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbQBqAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXABuAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAbgBNAG0AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcAG4ATQBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBsAGEAcwBzACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUACwAXABuACAAIAAgACAAUwBVAE0AKABNAGoAbQBUACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUADEALAAgAE0AagBtAFQAMgAsAFwAbgAgACAAIAAgACAAUwBVAE0AKABNAGoAbQBUADEALAAgAE0AagBtAFQAMgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBtAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBtAGoAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAbQBUAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AagBtAFQAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgAMwApACAAYQBuAGQAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAE0AagBtACAAaQBuAHQAbwAgAE0AagBtAFQAMQAgAGEAbgBkACAATQBqAG0AVAAyACAAZgBvAHIAIABzAHQAYQBnAGUAIAAxACAAYQBuAGQAIAAyACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AaQBqAG0AVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBGAFYAUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBqACwAIABGAFYAUwBqAG0AVAAxACwAIABNAEMARgBpAG0ALAAgAEIATwAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAagAgACoAIABGAFYAUwBqAG0AVAAxACAAKgAgAE0AQwBGAGkAbQAgACoAIABCAE8AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBWAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADEAIAAoADQAKQAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAFYAUwBqAG0AVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAHAAcgBpAG8AcgAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAZQBwAGEAcgBhAHQAaQBvAG4AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATQBNAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAcAByAGkAbwByACAAdABvACAAcwBvAGwAaQBkACAAcwBlAHAAYQByAGEAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAbQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXABuAEYAVgBTAGoAbQA0AFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0ANABUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBNAFMAagBtADEANwA5AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAE0ATQBTACAAMQAsACAANwAsACAAYQBuAGQAIAA5ACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AUwBTAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAIABNAE0AUwBqAG0AMQA3ADkAVAAxACwAIABTAFMAbQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIAAoAE0ATQBTAGoAbQAxADcAOQBUADEAIAAqACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAATQBNAFMAagBtAFQAMQBfADMALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAUwBTAGoAbQBUADEAXwAyACwAIABTAFMAagBtAFQAMQBfADMALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAUwBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMQAgACoAIABTAFMAagBtAFQAMQBfADEAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMwAgACoAIABTAFMAagBtAFQAMQBfADMAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwA1ACAAKgAgAFMAUwBqAG0AVAAxAF8ANQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQAxACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA3ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0ANwAsAFQAPQAxAH0AKQArACgATQBNAFMAXwB7AGoALABtAD0AOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADkALABUAD0AMQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQA0AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQAxADcAOQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBTAG0AXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAGUAcQB1AGEAdABpAG8AbgAgAGYAbwByACAATQBNAFMAbQA9ADEALAA3ACwAOQAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABpAHQAZQBtAHMAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcACIAKQA7AFwAbgAgACAAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABlAGEAYwBoACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0AaQBqAG0AVAAyAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAVABqAG0AVAAyACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAGkAIAA9ACAAcwB0AGEAdABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAAQgBPACwAIABNAE0AUwBqAG0AVAAyACwAIABNAEMARgBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAVgBTAFQAagBtAFQAMgApACwAIABWAFMAVABqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBNAFMAagBtAFQAMgApACwAIABNAE0AUwBqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAgACoAIABCAE8AIAAqACAATQBNAFMAagBtAFQAMgAgACoAIABNAEMARgBpAG0AIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAXAAiACwAXAAiAE0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgCwAEMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4AVgBTAFQAaQBqAG0AVAAyAFwAbgBrAGcAIABWAFMAXABuAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARgBWAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBWAFMATABtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAFYAUwBMAG0AVAAxACwAXABuACAAIAAgACAAVgBTAGoAIAAqACAARgBWAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAVgBTAEwAbQBUADEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANAApACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMATABtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AagBtACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEUARgBfAGoAbQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAyACkAKAA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAbQBcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AVAAxAFwAbgBrAGcAIABOAFwAbgBNAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBqAG0ALABUAD0AMQB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4AKQBcAG4ARgBOAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAARgBOAF8AagBtAFQAMQAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAARgBOAF8AagBtAFQAMQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AGoAbQAsAFQAPQAxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBfAGoAXAAiACwAIABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AXwBqAG0AVAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAzACkAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAKQBcAG4ARgBOAF8AagBtAFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMATgBfAHsAbQB9ACkAXABuAE0ATQBTAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4AUwBOAF8AbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACwAIABTAE4AXwBtACwAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABTAE4AXwBtACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBOAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAE4AXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBOAF8AagBtADQAVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAbgBNAE0AUwBfAGoAbQA0AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcAG4ATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAGwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADEALAA3ACwAOQApAFwAbgBTAE4AXwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALAAgAE0ATQBTAF8AagBtADEANwA5AFQAMQAsACAAUwBOAF8AbQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAKgAgAFMATgBfAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxAF8AMQAsACAATQBNAFMAagBtAFQAMQBfADIALAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIABNAE0AUwBqAG0AVAAxAF8ANAAsACAATQBNAFMAagBtAFQAMQBfADUALABcAG4AIAAgACAAIABTAFMAagBtAFQAMQBfADEALAAgAFMAUwBqAG0AVAAxAF8AMgAsACAAUwBTAGoAbQBUADEAXwAzACwAIABTAFMAagBtAFQAMQBfADQALAAgAFMAUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAagBtAFQAMQBfADEAIAAqACAAUwBTAGoAbQBUADEAXwAxACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIAAoAE0ATQBTAGoAbQBUADEAXwAzACAAKgAgAFMAUwBqAG0AVAAxAF8AMwApACAAKwAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8ANQAgACoAIABTAFMAagBtAFQAMQBfADUAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AewBqAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADEALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADcALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA3ACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AOQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQA0AFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQAxADcAOQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAbABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzACAAKABtAD0AMQAsADcALAA5ACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBOAF8AbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABTAHAAbABpAHQAIABlAHEAdQBhAHQAaQBvAG4AIABmAG8AcgAgAE0ATQBTAG0APQAxACwANwAsADkAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAaQB0AGUAbQBzACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAFcAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAAoAGgAZQBhAGQAKQBcAG4ATgBXAF8AagAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAHIAbwBkAHUAYwBlAGQAIABpAG4AIABzAHcAaQBuAGUAIABtAGEAbgB1AHIAZQAgAGEAbgBkACAAdwBhAHMAdABlACAAZgBlAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcAAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4AVwBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBXAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBXAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVwBfAGoAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcAByAG8AZAB1AGMAZQBkACAAaQBuACAAcwB3AGkAbgBlACAAbQBhAG4AdQByAGUAIABhAG4AZAAgAHcAYQBzAHQAZQAgAGYAZQBlAGQAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAcwB3AGkAbgBlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAsACAATQBNAFMAXwBqAG0AVAAyACwAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAgACoAIABNAE0AUwBfAGoAbQBUADIAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQAsAFQAPQAyAH0APQBOAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE4AVABfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE4AVABfAHsAagBtACwAVAA9ADIAfQA9AE0ATgBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQAsAFQAPQAxAH0ALQBFAEYAXwB7AG0ALABUAD0AMQB9ACkAXABuAE0ATgBfAGoAbQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ARQBGAF8AbQBUADEAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMQAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAxACwAIABFAEYAXwBtAFQAMQAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBtAFQAMQAgAC0AIABFAEYAXwBtAFQAMQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AewBqAG0ALABUAD0AMgB9AD0ATQBOAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtACwAVAA9ADEAfQAtAEUARgBfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAxAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGEAdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADUAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABEAGUAcABvAHMAaQB0AGkAbwBuACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXABuAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAbgBFAF8ATgAyAE8ATQBNAFMAYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAEEAVABNAE8AUwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAE0ATQBTAGEAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGEAZAB9AD0ATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AQQBUAE0ATwBTAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA1ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXABuAFQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwBcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBHAEEAUwBNAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADIAKQAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4ANwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEwAZQBhAGMAaABpAG4AZwAgAEEAbgBkACAAUgB1AG4AbwBmAGYAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAFwAbgBBAG4AbgB1AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZQBhAGMAaAAgAE0ATQBTAFwAbgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAE4ATABlAGEAYwBoAF8AewBqAG0APQA1AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEQAdQBlACAAdABvACAAcwB0AHIAaQBjAHQAIABlAG4AdgBpAHIAbwBuAG0AZQBuAHQAYQBsACAAYwBvAG4AdAByAG8AbABzACwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGEAcgBlACAAZQBzAHQAaQBtAGEAdABlAGQAIABvAG4AbAB5ACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABtAD0ANQApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGUAYQBjAGgAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAXABuAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBXAEUAVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMAVwBFAFQALAAgAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACwAXABuACAAIAAgACAATQBOAF8AagBtADUAVAAxACAAKgAgAEYAcgBhAGMAVwBFAFQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIALAAgAEUARgBfAG0AVAAyACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAsACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACkAIAAtACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA3ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABwAGkAZwBnAGUAcgB5ACAAYgBvAHUAbgBkAGEAcgB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcABpAGcAZwBlAHIAeQAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAsACAARQBGAF8AbQBUADIALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACwAIABNAE4ATABlAGEAYwBoAF8AagBtADUALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAKQAgAC0AIABNAE4ATABlAGEAYwBoAF8AagBtADUAKQAgACoAIAAoADEAIAAtACAAUABGACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABGAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18160,12 +18117,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18190,9 +18144,12 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/3_5_Enteric_Swine_WIP_v01.xlsx
+++ b/Excel/3_5_Enteric_Swine_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8374A056-2AC0-426F-BFF4-EDDC4674F26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D09F74E-6AFB-4A15-95E7-CE41317E76E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="390" windowWidth="28545" windowHeight="16950" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,10 +20,13 @@
     <sheet name="Input - Swine" sheetId="70" r:id="rId5"/>
     <sheet name="3.5.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Swine" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="106" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="111" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -104,6 +107,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title">_xlfn.LAMBDA("Emission factor for organic fertiliser and crop residues returned to the soil")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
@@ -580,7 +590,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="174">
   <si>
     <t>Home</t>
   </si>
@@ -1145,6 +1155,12 @@
   </si>
   <si>
     <t>Average liveweight (kg)</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2131,7 @@
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2457,9 +2473,6 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="37">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="71">
     <cellStyle name="Alert" xfId="62" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2534,241 +2547,7 @@
     <cellStyle name="Variable type input" xfId="66" xr:uid="{4F3E1D36-2125-457B-B28B-DAF403FCF3B5}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{537B7826-A596-42BB-BEEC-7984101BDA99}"/>
   </cellStyles>
-  <dxfs count="91">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="92">
     <dxf>
       <font>
         <b val="0"/>
@@ -3635,6 +3414,264 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4339,20 +4376,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="totalRow" dxfId="88"/>
-      <tableStyleElement type="firstColumn" dxfId="87"/>
-      <tableStyleElement type="firstRowStripe" dxfId="86"/>
-      <tableStyleElement type="secondRowStripe" dxfId="85"/>
+      <tableStyleElement type="wholeTable" dxfId="91"/>
+      <tableStyleElement type="headerRow" dxfId="90"/>
+      <tableStyleElement type="totalRow" dxfId="89"/>
+      <tableStyleElement type="firstColumn" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="totalRow" dxfId="82"/>
-      <tableStyleElement type="firstColumn" dxfId="81"/>
-      <tableStyleElement type="firstRowStripe" dxfId="80"/>
-      <tableStyleElement type="secondRowStripe" dxfId="79"/>
+      <tableStyleElement type="wholeTable" dxfId="85"/>
+      <tableStyleElement type="headerRow" dxfId="84"/>
+      <tableStyleElement type="totalRow" dxfId="83"/>
+      <tableStyleElement type="firstColumn" dxfId="82"/>
+      <tableStyleElement type="firstRowStripe" dxfId="81"/>
+      <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5923,6 +5960,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5997,7 +6054,7 @@
     <tableColumn id="1" xr3:uid="{A1AC17BE-6F0C-4EA3-88D1-F15B8A0AA6A1}" name="Class">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_VolatileSolids_Data(), Table_SourceData_Swine_VolatileSolids[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{539845C7-E401-474C-86C5-B676BBD1B040}" name="VSj" dataDxfId="78" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{539845C7-E401-474C-86C5-B676BBD1B040}" name="VSj" dataDxfId="79" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_VolatileSolids_Data(), Table_SourceData_Swine_VolatileSolids[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6028,20 +6085,20 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}" name="Table_SourceData_Swine_FracGASM28" displayName="Table_SourceData_Swine_FracGASM28" ref="D111:F117" totalsRowShown="0" dataDxfId="60" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}" name="Table_SourceData_Swine_FracGASM28" displayName="Table_SourceData_Swine_FracGASM28" ref="D111:F117" totalsRowShown="0" dataDxfId="61" dataCellStyle="Content normal">
   <autoFilter ref="D111:F117" xr:uid="{1333872B-E46C-4DC7-8E2D-1F3D704794C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6DD7EF85-D333-4B03-BD58-78D84BEEC9B4}" name="MMSm" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{6DD7EF85-D333-4B03-BD58-78D84BEEC9B4}" name="MMSm" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F61F4819-1794-4A31-843F-5F15C9F3C95F}" name="EFmT" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F61F4819-1794-4A31-843F-5F15C9F3C95F}" name="EFmT" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B97B38DF-3EA9-445C-BD0D-2CBB24B993D8}" name="NIR reference" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B97B38DF-3EA9-445C-BD0D-2CBB24B993D8}" name="NIR reference" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Data(), Table_SourceData_Swine_FracGASM28[[#Headers],[MMSm]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6085,7 +6142,7 @@
     <tableColumn id="1" xr3:uid="{39C5E3A8-688C-4C4E-A337-E32C77B7769F}" name="Livestock type j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{37866161-8EEC-44E3-8B1D-0210A7AFC89C}" name="Average liveweight (kg)" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{37866161-8EEC-44E3-8B1D-0210A7AFC89C}" name="Average liveweight (kg)" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6094,20 +6151,20 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{E6E3ED7D-B9CD-4192-B821-5B419D60F230}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{AFE7C1E4-6403-4F28-8209-832F1AE00903}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7C2EA6C-D25D-4C33-AEA0-CA7B250E39E2}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{2D532CE6-BB01-450D-82A5-4C5F5071B974}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1C767934-3B57-475F-9043-61B46B4B44B2}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{11D9C92F-5B95-434F-B380-92F3F9C84F63}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E2EA12E4-9CF6-4C68-A5D0-F05AC4B8A9F1}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{436AF3A4-282F-4168-AE14-E98FF20F57F7}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6116,12 +6173,12 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{CE2EC9E8-0E91-4093-A370-A0FB47853ED2}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{1197A506-7935-41B3-8230-B300726C222A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{B100C6B8-0EEF-4141-89C3-B97B70A5239A}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{35738AA9-632B-4C74-9D86-4BAD4DA2E81A}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6130,16 +6187,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{32197674-F4EC-40C4-BA61-58B06682F8E5}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D38E4CD-E2F7-4D92-8059-A8D9C3FB099F}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE6DB2AF-8B82-435D-A79B-8205BD960246}" name="Gas">
+    <tableColumn id="1" xr3:uid="{448C98E8-EAEE-4BB5-AE30-B9802D4D981B}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C1872EA8-E6F7-4CDB-BE15-139748243EE5}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{93CF53E3-F464-47C1-897F-B9311C8FF9C8}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6148,7 +6205,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{A03DACCB-4A75-40B0-8551-2B1D21A46594}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{C4EF3134-C3BD-4FF1-B7B7-86B42D5A5996}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6157,19 +6214,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00D8DCA3-10F5-4031-86FD-216D8A755B9E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{2576FED0-D49E-4EA9-9A03-D0FC13940F55}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A53FF128-FAFA-48C3-8A6E-8E78B89CFD95}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{15A82B2D-6B0A-43E6-AEF4-04032F3DC0D2}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F83400CF-8874-42E5-9041-D872244B9CFA}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{DD412816-A312-431D-A60F-0BED39BF8419}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CA87A7E6-25FB-4F61-B2BC-8876667D6A15}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{402C148D-4452-40B9-B0C1-B4ECD0E32D41}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4E372DE5-34A1-40F8-8BF5-A80188384573}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{C93A95A1-ACE1-4160-B5CF-B8372DA696A5}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6178,7 +6235,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{95132B17-5458-42C3-9E74-261F277F6664}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{929108B1-63BF-49B8-84F2-4B403185B845}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6198,52 +6255,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{55DB17EF-0F05-492B-8DF4-50777CFB302F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{F5208ADB-AB67-424E-9610-88B03E061E92}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C5C83B84-0235-4B48-9882-D789359978A3}" name="MAT" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{38E3AD1B-BF36-4E90-9194-0A97F43A8CCC}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2427DEBF-B9EF-405D-977C-D0B2800FCBB1}" name="MAP" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{91072CD8-03C6-4958-A23B-B0D84C9C352E}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EBA92C07-A154-437D-BDD5-52695464C73C}" name="Frost days per year" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{268A89E4-1746-4A51-920B-F71452A096F3}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{99735E8A-3D39-449D-A7C0-CD9B7DAE3957}" name="Elevation" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{908B4CD0-2C1B-4AD9-A1A1-EBD1B6FBAD7C}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B79F49BE-04C8-4800-9DCB-948081BBD991}" name="MAP:PET" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{638FCDF6-2767-41AF-A9B3-769093267947}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{223EBFAE-1287-4A0A-AA3E-9342D3BF4364}" name="Min temp" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{9BC8C8C3-DEE0-439D-9B9F-EAFE57C3BE6A}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{351C7274-AFD2-4546-A140-A95A456892E8}" name="Max temp" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{C5C205E9-12AD-4BAB-81D2-6269B4CA42FD}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C74C0D42-AEEA-4278-AD59-0334EC505CEC}" name="Min rainfall" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4C2AD9FA-A38E-4AAF-9D27-83303336A667}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8B3776A6-D901-494F-A436-67BB3CB20929}" name="Max rainfall" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{67D95C8B-A269-45F0-9275-5211320DB362}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{29781557-BEE7-4BC2-8FCF-88051FE8BA04}" name="Min frost days" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{A0E7C898-2974-4E85-BB2E-30080780280A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{226D5EA0-8392-496D-B07B-0115FF6685C1}" name="Max frost days" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{68582EF7-292E-43E8-B12C-6C40E9E44480}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{97FCC930-F093-4ED4-A18F-679D2FFE3417}" name="Min elevation" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C557A0C2-7B9F-4000-B29C-C828F4F36848}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{2B589B12-9689-4C72-B4ED-6C287BBF0233}" name="Max elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{A86C5190-21D7-4D40-A97C-5B445BB2036C}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D7A13881-2DB8-4008-8FA2-574069DAD6F6}" name="Min MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{BAE9AE1A-A75C-426E-B3EC-0EF06EF3F2C4}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2145277F-3B0D-4FA7-97B5-A7338EBFBA01}" name="Max MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{AC011845-7B1F-4BA8-89AC-5ACAF083B4CF}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6269,31 +6326,31 @@
     <tableColumn id="1" xr3:uid="{948C8C81-0F25-4404-945E-CD16BE93BFBF}" name="MMS">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="77" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="76" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="75" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="74" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="73" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="74" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="72" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="73" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="71" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="72" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="70" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="71" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="69" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="70" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6302,16 +6359,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{02E9396F-7D92-4EBB-887B-ADD206B4ADDF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{5024A430-4358-4862-A0D1-3E6B0BAD7FCF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7C9BA32D-00D8-4C52-9DF7-220AA12DE65F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{6CC59E7C-AE08-43FD-A31D-1A6E0235C014}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A81E5122-308B-41E4-B622-AE4C693CCA35}" name="Wet or Dry Zone" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{4987A5F9-4B8D-4E60-B52C-68584596258B}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6320,7 +6377,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{1A688357-E7C3-4A2A-B4D3-A0F24B08E305}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{66572D4F-9577-49BD-BA42-9BD8E68CA26A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6328,16 +6385,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C8403960-4434-43CD-ABBE-E8DF4D86B9F5}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{8C4B8E77-7937-4A5D-85FD-4F874DB5D2E6}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66A4AD83-37E6-4BCB-BC66-B572872B5198}" name="MAT">
+    <tableColumn id="2" xr3:uid="{DF85DD65-FC08-4D95-936C-60DD52C7EEA7}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B9291C4C-E6A7-4495-A3EE-77DAB17978C7}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{4852D7C1-94B2-4D26-8033-D554A00D0931}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3C13F341-9CBC-46A8-BC68-8C55D43C9398}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{CFCC2F62-8E85-4C13-B9D2-68774CB5913A}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6346,7 +6403,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{8CCA099A-1815-4C9E-8BE1-EAFCEA3125C3}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{871A7457-184A-4DF9-A3C5-0944D54E75DD}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6354,16 +6411,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BF4D7F70-B372-4198-B448-F69D7AB5C57A}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{E638BB52-31C0-4EF8-A90A-F41CE0D2834B}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0636C224-96C6-4792-91A4-1FC86B7BC2BB}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{3CD24968-FDB5-497B-A158-15286E286D1E}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{58B0F4F3-EB24-4A00-9F9A-0E64F1E2D5D0}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{9AE88C75-6949-4F97-8928-8337300C60CC}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CB6299EC-5E20-4209-BE64-AC6EDA2A45BF}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{A44B45C8-BE9C-4FCD-8234-8788F85C5EBA}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6372,16 +6429,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{E1D1277F-7083-467C-A78B-B5A5473D3374}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{C633F88A-C685-44BB-A3EE-C6B89CE66B01}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A5866685-43DA-480D-AE27-DAD823223B61}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{FB8B09E6-F484-4A86-A9C6-90DBEF46CDC3}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92ECD4D2-81B9-467C-BA67-C008BE7F8F21}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{A1809FC1-8018-4DCD-A52B-1DA0CAC5B4F8}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6390,16 +6447,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C757BE5D-8986-486B-9942-45BFD29D0636}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{8A036A35-AA22-45C8-805D-7446A3204215}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{71FE53BA-D360-4C24-8E5B-28CB3F969908}" name="Data source">
+    <tableColumn id="1" xr3:uid="{1D024494-6163-4F0F-BA5A-E834E375B384}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{58F6D1E3-6B78-4718-A383-427BF82805E4}" name="Data score">
+    <tableColumn id="2" xr3:uid="{3F3D40FA-4AE9-4F0F-AC21-B0494BFFE2C7}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6408,16 +6465,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{AD5BAE0A-AE6C-4E5D-9102-8C3D108836A9}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{AC741027-A191-4BA5-8392-BD05E5C97933}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BC669E04-ED77-44FE-9D5F-8C8107EB4A98}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{C84962BF-DBD8-4300-88E3-CD132FF3D28F}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A3948F95-F1C4-45B3-81A4-39D322485349}" name="FracWET" dataDxfId="40">
+    <tableColumn id="2" xr3:uid="{45408FAE-2E1A-4F9E-935A-9EE4FD8DCFDC}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6426,7 +6483,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{77B971EA-407C-45A5-9FFB-F7AA722C8E08}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{8A3018CF-409A-41E0-A723-AAD8BC61E31F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6435,19 +6492,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A2F3F9BB-DA9E-4193-9F8B-B6A61E653CCF}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{79601505-6D4E-400E-A1DE-A467E131BB51}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3D22419F-B45A-49E4-9B2C-61DFA559A5E6}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{DB77EB4C-F64D-434D-985D-329ADE774551}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25D60932-977A-4B69-B269-FC2D0FBEF5FD}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{E58C180B-3E8D-4978-A361-B4177B2154B0}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C0A42ED4-5BEF-4593-8E87-70CB6EE0301D}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{45292F44-DB1C-473B-8E4C-0D42689301B4}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{782D7ADE-E7B1-4141-A25C-555CE2F063CD}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{091C0121-3FD8-4516-8796-4304279C22EC}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6456,16 +6513,16 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{4FD55417-029C-4CE1-94B5-7F7CCA88A962}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{84C0127D-61A6-4925-A00C-3911104EADE3}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5AEF521B-87A4-4DF0-9061-A42BD804FA47}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{693D3EBC-D313-455E-8D6A-56FC5DF1709D}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{413EF7D5-6C1D-48C4-ADE3-C2FBFE9CDBF0}" name="FracWET" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BD31B215-616A-4C84-8CFD-6DB3A05B7C26}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6474,16 +6531,16 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{6D0385FD-EFA3-4C84-B44D-9F37B1305043}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{C4B125E7-70AC-4B80-8F51-838964148C1D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{24B3DD1A-762C-4056-B47D-C7F4C3D2140D}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{AC69701C-ADD7-445E-8E02-EFF2E966855C}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7FA3D3B2-F03B-4A49-B036-1E6713C6C2BA}" name="EFPRP" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{49530B33-FBD8-471E-9119-E87F5F88B0DC}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6492,16 +6549,16 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{D7CF299F-EB3B-4475-B57E-88E228BFA01A}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F3ED0C8C-81A6-4000-B7C7-04FE4E47E2C1}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{891AEBD9-B5D9-477E-A4F8-180604EEEB5F}" name="Month">
+    <tableColumn id="1" xr3:uid="{390C890A-725C-471C-9DBD-973AB078E517}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{68A7ECE7-9AF7-4FB2-8EBA-0AF2F740F298}" name="Season" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA65B608-F63D-4802-8F24-7BF9C115E410}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6524,7 +6581,7 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{55A68CD2-471B-4B4F-9D5E-65C39267BD6F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{9A2CC4FB-6B00-4D6B-ABB1-2DAAC0801EDA}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6544,52 +6601,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{36D78F8A-058B-42CA-B726-7AEBBCA6C28C}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{5DD475A6-4779-4397-B04C-3DD211336AE3}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1091063A-29C3-4F2A-BFEF-BD86006AD144}" name="MAT (ºC)" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F0FFFA46-5867-4CA9-A601-600D6D8791AA}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D8D6B89D-F8F7-4100-9AC6-7433F92DE90E}" name="Anaerobic lagoon" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0FE9A949-37B5-4E2A-850E-CD3CFC8CA39D}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5AD0EE1F-0F8D-4B1E-BC41-D905561F457C}" name="Digester / covered lagoons" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{568F0EC3-AE1C-4B69-AC3C-DF3CF2B8EB53}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{70A47EB3-89E9-49EA-A584-4FFFF617FFFE}" name="Liquid systems" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{29AF04BF-2503-45F0-839D-62669663EDF4}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6379D57A-CF72-4017-8026-7368D62E7C6E}" name="Daily spread" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{40408AF4-074F-4536-8987-A979EDB33EFA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A8CAA5F5-A9E2-490C-8E9E-F98FEC2B85B7}" name="Composting (passive windrow)" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{76EFC40F-B134-4098-A6E1-384C95509312}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2932A796-896E-4749-8473-D4D99CB5A8DA}" name="Solid storage" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{9B9A3939-3C54-4700-9044-43185125F7C7}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B15FC1CD-D6D4-48C6-BB02-0784024F60E1}" name="Pit storage" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{C2F77327-DCEF-46C5-8D5C-4306D9CD24CC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BEBE432B-3D78-4900-9DC3-1FD9ACCBB17C}" name="Deep litter" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C87FBABE-679E-43BB-89A2-424C9BCC4BD7}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{A81D0680-FD86-4172-B5F0-E4CCA7F0900F}" name="Poultry manure with bedding" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{0AB69F11-96F2-4BF6-82B9-629DE6CD5F31}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BE403667-5932-4CF5-8344-621BAA196406}" name="Poultry manure without bedding" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{1B6C7C98-4101-4C77-890D-CA66FFB388A6}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D72C37E3-C784-49F8-9FFA-148700905D66}" name="Direct processing" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CFD2DBE9-22EC-4983-9CFF-196FBBFB1F7A}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FECAD450-29C4-40CA-9D51-7672268D9D32}" name="Direct application" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{C6B1B156-02AF-431D-970E-393824427494}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3BCC1851-11A9-41A2-B4BC-E7AFBD1EAA84}" name="Pasture range and paddock" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{356060D5-42C5-4106-BF08-8C76DEBF354C}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{69CC47FE-434C-431F-B727-358EA13CFB6F}" name="MAT raw" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{6E743D72-942F-40D0-BDC1-893034B69FC4}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6598,6 +6655,24 @@
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{20C8760A-30DA-4C92-8800-368E5F2E7CFA}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5F923D5D-512C-4BDC-828E-D197B29189C9}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A98E1055-49EA-4931-B52D-245A088FC117}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
   <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6676,7 +6751,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}" name="Table_SourceData_Swine_NitrogenInWaste" displayName="Table_SourceData_Swine_NitrogenInWaste" ref="D89:G93" totalsRowShown="0" dataDxfId="68" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}" name="Table_SourceData_Swine_NitrogenInWaste" displayName="Table_SourceData_Swine_NitrogenInWaste" ref="D89:G93" totalsRowShown="0" dataDxfId="69" dataCellStyle="Content normal">
   <autoFilter ref="D89:G93" xr:uid="{61D86DCB-D80D-4593-96F3-A897FC93073F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6684,16 +6759,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1C4094D2-E798-4EA4-8FBC-50FBA0E527D4}" name="Class" dataDxfId="67" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{1C4094D2-E798-4EA4-8FBC-50FBA0E527D4}" name="Class" dataDxfId="68" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BD1910A-3F15-4C45-9A95-D2ADDB197E82}" name="NWj" dataDxfId="66" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BD1910A-3F15-4C45-9A95-D2ADDB197E82}" name="NWj" dataDxfId="67" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06D949C0-1431-4E8B-9FED-E08C8D4D7E61}" name="NWj Daily" dataDxfId="65" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{06D949C0-1431-4E8B-9FED-E08C8D4D7E61}" name="NWj Daily" dataDxfId="66" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5C9C6F5B-830D-4A53-BEF6-FDE389E9F8CC}" name="Class name" dataDxfId="64" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5C9C6F5B-830D-4A53-BEF6-FDE389E9F8CC}" name="Class name" dataDxfId="65" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_NitrogenInWaste_Data(), Table_SourceData_Swine_NitrogenInWaste[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6702,16 +6777,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}" name="Table_SourceData_Swine_FeedIntake" displayName="Table_SourceData_Swine_FeedIntake" ref="D78:E82" totalsRowShown="0" dataDxfId="63" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}" name="Table_SourceData_Swine_FeedIntake" displayName="Table_SourceData_Swine_FeedIntake" ref="D78:E82" totalsRowShown="0" dataDxfId="64" dataCellStyle="Content normal">
   <autoFilter ref="D78:E82" xr:uid="{E34928EB-73E5-43B2-830B-089F30DA4EF0}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CAC8EB28-568F-4E9F-8E36-EBDFF74A58D3}" name="Class" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{CAC8EB28-568F-4E9F-8E36-EBDFF74A58D3}" name="Class" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_FeedIntake_Data(), Table_SourceData_Swine_FeedIntake[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2CE09F11-701B-40A5-9E2D-B745C440FD8B}" name="Ij" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2CE09F11-701B-40A5-9E2D-B745C440FD8B}" name="Ij" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_FeedIntake_Data(), Table_SourceData_Swine_FeedIntake[[#Headers],[Class]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9705,107 +9780,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E205:G205">
-    <cfRule type="cellIs" dxfId="21" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F40:F41">
-    <cfRule type="cellIs" dxfId="20" priority="69" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="69" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="cellIs" dxfId="19" priority="68" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="68" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="cellIs" dxfId="18" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121:F122">
-    <cfRule type="cellIs" dxfId="17" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133:F134">
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F145:F146">
-    <cfRule type="cellIs" dxfId="15" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F157:F158">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F245:F246">
-    <cfRule type="cellIs" dxfId="13" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="12" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="11" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F279:F280">
-    <cfRule type="cellIs" dxfId="10" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="9" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="8" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29:I34">
-    <cfRule type="cellIs" dxfId="7" priority="55" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="55" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I55:I59">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:I66">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I70:I73">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I77:I80">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I88">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:L43 I48:I51 J101 I119 I199 I205">
-    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="74" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12430,21 +12505,21 @@
       <c r="V126" s="1"/>
     </row>
     <row r="127" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D127" s="126" t="s">
+      <c r="D127" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="E127" s="126" t="s">
+      <c r="E127" s="34" t="s">
         <v>171</v>
       </c>
       <c r="M127" s="1"/>
       <c r="V127" s="1"/>
     </row>
     <row r="128" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D128" s="126" t="str" cm="1">
+      <c r="D128" s="34" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
         <v>Sows</v>
       </c>
-      <c r="E128" s="126" cm="1">
+      <c r="E128" s="34" cm="1">
         <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_AverageLiveweight_Data(),Table_SourceData_Swine_Liveweight[[#Headers],[Livestock type j]],0)</f>
         <v>188</v>
       </c>
@@ -13479,8 +13554,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E1428C-4DC5-4BD6-BBEB-2A47208D1A43}">
-  <dimension ref="A1:BY250"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04C81B2-B774-4D14-903C-7E20E202643E}">
+  <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
@@ -14883,31 +14958,31 @@
       </c>
       <c r="T97" s="34"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="49" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="49" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="49" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="49" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="49" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="49" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="49"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="49"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -16084,7 +16159,10 @@
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D229" s="50"/>
+      <c r="D229" s="50" t="str" cm="1">
+        <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
+        <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
+      </c>
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D231" s="34" t="s">
@@ -17390,10 +17468,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="6" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="49" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E257" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="34" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="34" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="34" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="16">
+  <tableParts count="17">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -17410,6 +17540,7 @@
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17899,7 +18030,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABTAHcAaQBuAGUAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXABuAFYAUwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAKABWAFMAagApACAALQAgADIAMAAyADAAIAB0AG8AIAAyADAAMgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE8AbgBsAHkAIAB1AHMAZQBzACAAZABhAHQAYQAgAGYAbwByACAAMgAwADIAMAAtADIAMAAyADQALgAgAFUAcwBlACAAJwBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAJwAgAGQAYQB0AGEAIABmAG8AcgAgACcATwB0AGgAZQByACAAagA9ADQAJwAgAGMAbABhAHMAcwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABhAHMAcwBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMAAuADQAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsACAAMAAuADQANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGkAbAB0AHMAXAAiACwAIAAwAC4ANQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzAFwAIgAsACAAMAAuADMAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAFwAbgBJAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAEYAZQBlAGQAIABpAG4AdABhAGsAZQAgAC0AIABpAG4AZwBlAHMAdABlAGQAIABhAHMAIABmAGUAZAAgACAAKABJAGoAKQAgAC0AIAAyADAAMgAwACAAdABvACAAMgAwADIANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABPAG4AbAB5ACAAdQBzAGUAcwAgAGQAYQB0AGEAIABmAG8AcgAgADIAMAAyADAALQAyADAAMgA0AC4AIABVAHMAZQAgACcAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzACcAIABkAGEAdABhACAAZgBvAHIAIAAnAE8AdABoAGUAcgAgAGoAPQA0ACcAIABjAGwAYQBzAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAEkAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMgAuADYAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADIALgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMgAuADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAcwBcACIALAAgADEALgA3ADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBcAG4ATgBXAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB3AGEAcwB0AGUAIAAoAE4AVwBqACkAIAAtACAAMgAwADIAMAAgAHQAbwAgADIAMAAyADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATwBuAGwAeQAgAHUAcwBlAHMAIABkAGEAdABhACAAZgBvAHIAIAAyADAAMgAwAC0AMgAwADIANAAuACAAVQBzAGUAIAAnAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwAnACAAZABhAHQAYQAgAGYAbwByACAAJwBPAHQAaABlAHIAIABqAD0ANAAnACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAE4AVwBqACAAZABhAGkAbAB5ACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAHAAcgBvAHYAaQBkAGUAIABkAGEAaQBsAHkAIAB2AGEAbAB1AGUAIABmAG8AcgAgAE8AdABoAGUAcgBzACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIAAnAEMAbABhAHMAcwAgAG4AYQBtAGUAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAE4AVwBqAFwAIgAsACAAXAAiAE4AVwBqACAAZABhAGkAbAB5AFwAIgAsACAAXAAiAEMAbABhAHMAcwAgAG4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADAALgAwADQANgAsACAAMAAuADAANAA2ACwAIABcACIAQgBvAGEAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADAALgAwADQAOQAsACAAMAAuADAANAA5ACwAIABcACIAUwBvAHcAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMAAuADAANAA2ACwAIAAwAC4AMAA0ADYALAAgAFwAIgBHAGkAbAB0AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgBzACAAKABrAGcALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAIgAsACAAMQAxAC4ANAAsACAAMAAuADAAMwAxADIALAAgAFwAIgBPAHQAaABlAHIAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUAFwAbgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMgA6ACAAUwB3AGkAbgBlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcATgApACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByACAAKABEAHIAeQAgAGwAbwB0ACkAXAAiACwAIAAwAC4AMwAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADEAMgA1ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALgA1ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AGUAcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAEYAcgBhAGMARwBBAFMATQBtAFQAXABuAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABFAEYAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBOADIATwAgAC0AIABOACAALwAgAGsAZwBOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMwA6ACAAUwB3AGkAbgBlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGIAeQAgAE0ATQBTACAAKABrAGcATgAyAE8ALQBOAC8AawBnAE4AKQAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAbQBcACIALAAgAFwAIgBFAEYAbQBUAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdQB0AGQAbwBvAHIAIAAoAEQAcgB5ACAAbABvAHQAKQBcACIALAAgADAALgAwADIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADEALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABvAGMAawBwAGkAbABlACAAKABTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMAAyACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQgAwAFwAbgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIABtAGUAdABoAGEAbgBlACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAoADIAMAAxADkAKQAsACAAQwBoAGEAcAB0AGUAcgAgADEAMAAgAFsANABdAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgA2AC4ANAA6ACAAUwB3AGkAbgBlACAALQAgAE0AQwBGAHMAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAAtACAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAEEAQwBUACwAIABzAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAxADAALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcAOAAsACAAMAAuADcAOAAsACAAMAAuADcANQAsACAAMAAuADcAMAAsACAAMAAuADcANAAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAZQByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAPAAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVwBjAG8AXABuAGsAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIAAtACAAQQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGkAbgB2AGUAbgB0AG8AcgB5ACAAZABlAGYAYQB1AGwAdABzACkAIAAoAGsAZwApACAAKABXAGMAbwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADUAOgAgAFMAdwBpAG4AZQAgAC0AIABBAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAaQBuAHYAZQBuAHQAbwByAHkAIABkAGUAZgBhAHUAbAB0AHMAKQAgACgAawBnACkAIAAoAFcAYwBvACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHcAcwBcACIALAAgADEAOAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADIAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAaQBsAHQAcwBcACIALAAgADEAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwBcACIALAAgADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAIABhAHQAIAB0AHUAcgBuAG8AZgBmAFwAIgAsACAAOQA3AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBcAG4ANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG4AdgBlAG4AdABpAG8AbgBhAGwAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByAC8AZgByAGUAZQAgAHIAYQBuAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBcAG4ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGUAeAB0ACAAcgBlAGYAZQByAHMAIAB0AG8AIAAnAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAJwAgAE0ATQBTACwAIABiAHUAdAAgAGUAcQB1AGEAdABpAG8AbgAgAHIAZQBmAGUAcgBzACAAdABvACAAJwBkAHIAeQBsAG8AdAAnACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAFwAbgBGAFwAbgBNAEoALwBrAGcAIABDAEgANABcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcAIABDAEgANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADUALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA1ADUALgAyADIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA1AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqACAAPQAgAHQAaABlACAAYQB2AGUAcgBhAGcAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAHkAcwAgAG8AbgAgAGYAYQByAG0AIABmAG8AcgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIAAoAE4AXwBqACAAKgAgAE0AXwBqACAAKgAgAEQAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAARABfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4ANQAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAdABoAGUAIABhAHYAZQByAGEAZwBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAeQBzACAAbwBuACAAZgBhAHIAbQAgAGYAbwByACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABvAGYAIABzAHcAaQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcAG4ASQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAZgBlAGUAZAAgAGkAbgBnAGUAcwB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBGACAAPQAgAG0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoAE0ASgAvAGsAZwAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAARgAsAFwAbgAgACAAIAAgACgASQBfAGoAIAAqACAAMQA4AC4ANgAgACoAIAAwAC4AMAAwADcAKQAgAC8AIABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQBcAFwAZgByAGEAYwB7AEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADgALgA2AFwAXAB0AGkAbQBlAHMAIAAwAC4AMAAwADcAfQB7AEYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABmAGUAZQBkACAAaQBuAGcAZQBzAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADgALgA2AFwAIgAsACAAXAAiAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAKABHAEUAKQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkAFwAIgAsACAAXAAiAE0ASgAgAEcARQAvAGsAZwAgAGYAZQBlAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAC4AMAAwADcAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAARwBFACAAaQBuAHQAYQBrAGUAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAG0AZQB0AGgAYQBuAGUAIABiAHkAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBcACIALAAgAFwAIgBtAGUAZwBhAGoAbwB1AGwAZQBzACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAE0ASgAvAGsAZwAgAEMASAA0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAAFCAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlACAAOgAgAGQAYQB5AHMAXABuAE0AbQBqACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAagAsACAATQBtAGoALAAgAE4AagAsAFwAbgAgACAAIAAgAEQAagAgACoAIABNAG0AagAgACoAIABOAGoAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGoAXAAiACwAXAAiAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbQBqAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXABuAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAbgBNAG0AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcAG4ATQBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBsAGEAcwBzACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUACwAXABuACAAIAAgACAAUwBVAE0AKABNAGoAbQBUACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUADEALAAgAE0AagBtAFQAMgAsAFwAbgAgACAAIAAgACAAUwBVAE0AKABNAGoAbQBUADEALAAgAE0AagBtAFQAMgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBtAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBtAGoAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAbQBUAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AagBtAFQAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgAMwApACAAYQBuAGQAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAE0AagBtACAAaQBuAHQAbwAgAE0AagBtAFQAMQAgAGEAbgBkACAATQBqAG0AVAAyACAAZgBvAHIAIABzAHQAYQBnAGUAIAAxACAAYQBuAGQAIAAyACAATQBNAFMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AaQBqAG0AVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBGAFYAUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBqACwAIABGAFYAUwBqAG0AVAAxACwAIABNAEMARgBpAG0ALAAgAEIATwAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAagAgACoAIABGAFYAUwBqAG0AVAAxACAAKgAgAE0AQwBGAGkAbQAgACoAIABCAE8AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBWAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADEAIAAoADQAKQAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAFYAUwBqAG0AVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAHAAcgBpAG8AcgAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAZQBwAGEAcgBhAHQAaQBvAG4AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATQBNAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAcAByAGkAbwByACAAdABvACAAcwBvAGwAaQBkACAAcwBlAHAAYQByAGEAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAbQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXABuAEYAVgBTAGoAbQA0AFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0ANABUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBNAFMAagBtADEANwA5AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAE0ATQBTACAAMQAsACAANwAsACAAYQBuAGQAIAA5ACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AUwBTAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAIABNAE0AUwBqAG0AMQA3ADkAVAAxACwAIABTAFMAbQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIAAoAE0ATQBTAGoAbQAxADcAOQBUADEAIAAqACAAUwBTAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAATQBNAFMAagBtAFQAMQBfADMALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAUwBTAGoAbQBUADEAXwAyACwAIABTAFMAagBtAFQAMQBfADMALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAUwBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMQAgACoAIABTAFMAagBtAFQAMQBfADEAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMwAgACoAIABTAFMAagBtAFQAMQBfADMAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwA1ACAAKgAgAFMAUwBqAG0AVAAxAF8ANQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQAxACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA3ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0ANwAsAFQAPQAxAH0AKQArACgATQBNAFMAXwB7AGoALABtAD0AOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADkALABUAD0AMQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQA0AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQAxADcAOQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBTAG0AXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAGUAcQB1AGEAdABpAG8AbgAgAGYAbwByACAATQBNAFMAbQA9ADEALAA3ACwAOQAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABpAHQAZQBtAHMAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcACIAKQA7AFwAbgAgACAAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABlAGEAYwBoACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0AaQBqAG0AVAAyAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAVABqAG0AVAAyACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAGkAIAA9ACAAcwB0AGEAdABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAAQgBPACwAIABNAE0AUwBqAG0AVAAyACwAIABNAEMARgBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAVgBTAFQAagBtAFQAMgApACwAIABWAFMAVABqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBNAFMAagBtAFQAMgApACwAIABNAE0AUwBqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBtAFQAMgAgACoAIABCAE8AIAAqACAATQBNAFMAagBtAFQAMgAgACoAIABNAEMARgBpAG0AIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAaQBqAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAXAAiACwAXAAiAE0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgCwAEMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4AVgBTAFQAaQBqAG0AVAAyAFwAbgBrAGcAIABWAFMAXABuAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARgBWAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBWAFMATABtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAFYAUwBMAG0AVAAxACwAXABuACAAIAAgACAAVgBTAGoAIAAqACAARgBWAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAVgBTAEwAbQBUADEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANAApACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMATABtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AagBtACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEUARgBfAGoAbQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAyACkAKAA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAbQBcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AVAAxAFwAbgBrAGcAIABOAFwAbgBNAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBqAG0ALABUAD0AMQB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4AKQBcAG4ARgBOAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAARgBOAF8AagBtAFQAMQAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAARgBOAF8AagBtAFQAMQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AGoAbQAsAFQAPQAxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBfAGoAXAAiACwAIABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AXwBqAG0AVAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAzACkAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAKQBcAG4ARgBOAF8AagBtAFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAE4AXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMATgBfAHsAbQB9ACkAXABuAE0ATQBTAF8AagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4AUwBOAF8AbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACwAIABTAE4AXwBtACwAXABuACAAIAAgACAATQBNAFMAXwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABTAE4AXwBtACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBOAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAE4AXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBOAF8AagBtADQAVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAbgBNAE0AUwBfAGoAbQA0AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcAG4ATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAGwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADEALAA3ACwAOQApAFwAbgBTAE4AXwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALAAgAE0ATQBTAF8AagBtADEANwA5AFQAMQAsACAAUwBOAF8AbQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAXwBqAG0AMQA3ADkAVAAxACAAKgAgAFMATgBfAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEALABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxAF8AMQAsACAATQBNAFMAagBtAFQAMQBfADIALAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIABNAE0AUwBqAG0AVAAxAF8ANAAsACAATQBNAFMAagBtAFQAMQBfADUALABcAG4AIAAgACAAIABTAFMAagBtAFQAMQBfADEALAAgAFMAUwBqAG0AVAAxAF8AMgAsACAAUwBTAGoAbQBUADEAXwAzACwAIABTAFMAagBtAFQAMQBfADQALAAgAFMAUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAE0ATQBTAF8AagBtADQAVAAxACAAKwAgACgATQBNAFMAagBtAFQAMQBfADEAIAAqACAAUwBTAGoAbQBUADEAXwAxACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIAAoAE0ATQBTAGoAbQBUADEAXwAzACAAKgAgAFMAUwBqAG0AVAAxAF8AMwApACAAKwAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8ANQAgACoAIABTAFMAagBtAFQAMQBfADUAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAGoAbQA0AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYATgBfAHsAagBtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqAG0APQAxACwANwAsADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAE4AXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AewBqAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADEALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADcALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA3ACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AOQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQA0AFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQAxADcAOQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAbABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzACAAKABtAD0AMQAsADcALAA5ACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBOAF8AbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABTAHAAbABpAHQAIABlAHEAdQBhAHQAaQBvAG4AIABmAG8AcgAgAE0ATQBTAG0APQAxACwANwAsADkAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAaQB0AGUAbQBzACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAFcAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAAoAGgAZQBhAGQAKQBcAG4ATgBXAF8AagAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAHIAbwBkAHUAYwBlAGQAIABpAG4AIABzAHcAaQBuAGUAIABtAGEAbgB1AHIAZQAgAGEAbgBkACAAdwBhAHMAdABlACAAZgBlAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAAoAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcAAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4AVwBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBXAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBXAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVwBfAGoAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcAByAG8AZAB1AGMAZQBkACAAaQBuACAAcwB3AGkAbgBlACAAbQBhAG4AdQByAGUAIABhAG4AZAAgAHcAYQBzAHQAZQAgAGYAZQBlAGQAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAcwB3AGkAbgBlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAsACAATQBNAFMAXwBqAG0AVAAyACwAXABuACAAIAAgACAATgBUAF8AagBtAFQAMgAgACoAIABNAE0AUwBfAGoAbQBUADIAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQAsAFQAPQAyAH0APQBOAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE4AVABfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE4AVABfAHsAagBtACwAVAA9ADIAfQA9AE0ATgBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQAsAFQAPQAxAH0ALQBFAEYAXwB7AG0ALABUAD0AMQB9ACkAXABuAE0ATgBfAGoAbQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ARQBGAF8AbQBUADEAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMQAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAxACwAIABFAEYAXwBtAFQAMQAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBtAFQAMQAgAC0AIABFAEYAXwBtAFQAMQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AewBqAG0ALABUAD0AMgB9AD0ATQBOAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtACwAVAA9ADEAfQAtAEUARgBfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAxAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGEAdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADUAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABEAGUAcABvAHMAaQB0AGkAbwBuACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXABuAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAbgBFAF8ATgAyAE8ATQBNAFMAYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAEEAVABNAE8AUwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAE0ATQBTAGEAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGEAZAB9AD0ATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AQQBUAE0ATwBTAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA1ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXABuAFQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwBcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBHAEEAUwBNAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARgByAGEAYwBHAEEAUwBNAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADIAKQAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4ANwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEwAZQBhAGMAaABpAG4AZwAgAEEAbgBkACAAUgB1AG4AbwBmAGYAIABOADIATwAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAFwAbgBBAG4AbgB1AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZQBhAGMAaAAgAE0ATQBTAFwAbgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAE4ATABlAGEAYwBoAF8AewBqAG0APQA1AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEQAdQBlACAAdABvACAAcwB0AHIAaQBjAHQAIABlAG4AdgBpAHIAbwBuAG0AZQBuAHQAYQBsACAAYwBvAG4AdAByAG8AbABzACwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGEAcgBlACAAZQBzAHQAaQBtAGEAdABlAGQAIABvAG4AbAB5ACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAKABtAD0ANQApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGUAYQBjAGgAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAXABuAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBXAEUAVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMAVwBFAFQALAAgAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACwAXABuACAAIAAgACAATQBOAF8AagBtADUAVAAxACAAKgAgAEYAcgBhAGMAVwBFAFQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQA9AE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAF8AewBNAFMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBNAE4ATABlAGEAYwBoAF8AagBtADUAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIALAAgAEUARgBfAG0AVAAyACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAsACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACkAIAAtACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9ACgATQBOAF8AewBqAG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyAH0AKQAtAE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgA3ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABwAGkAZwBnAGUAcgB5ACAAYgBvAHUAbgBkAGEAcgB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcABpAGcAZwBlAHIAeQAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAsACAARQBGAF8AbQBUADIALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACwAIABNAE4ATABlAGEAYwBoAF8AagBtADUALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAKQAgAC0AIABNAE4ATABlAGEAYwBoAF8AagBtADUAKQAgACoAIAAoADEAIAAtACAAUABGACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABGAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAEYAbwByACAAUwB3AGkAbgBlAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFwAbgBWAFMAagBcAG4AawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAKQAgAC0AIAAyADAAMgAwACAAdABvACAAMgAwADIANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgAxADoAIABTAHcAaQBuAGUAIAAtACAASQBuAHQAYQBrAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAFAAaQBnAEIAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABPAG4AbAB5ACAAdQBzAGUAcwAgAGQAYQB0AGEAIABmAG8AcgAgADIAMAAyADAALQAyADAAMgA0AC4AIABVAHMAZQAgAFwAdQAwADAAMgA3AFMAbABhAHUAZwBoAHQAZQByACAAcABpAGcAcwBcAHUAMAAwADIANwAgAGQAYQB0AGEAIABmAG8AcgAgAFwAdQAwADAAMgA3AE8AdABoAGUAcgAgAGoAPQA0AFwAdQAwADAAMgA3ACAAYwBsAGEAcwBzAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAFYAUwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAG8AYQByAHMAXAAiACwAIAAwAC4ANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB3AHMAXAAiACwAIAAwAC4ANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAaQBsAHQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByAHMAXAAiACwAIAAwAC4AMwA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEkAagBcAG4AawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIAAtACAARgBlAGUAZAAgAGkAbgB0AGEAawBlACAALQAgAGkAbgBnAGUAcwB0AGUAZAAgAGEAcwAgAGYAZQBkACAAIAAoAEkAagApACAALQAgADIAMAAyADAAIAB0AG8AIAAyADAAMgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMQA6ACAAUwB3AGkAbgBlACAALQAgAEkAbgB0AGEAawBlACAAYQBuAGQAIABtAGEAbgB1AHIAZQAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABQAGkAZwBCAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE8AbgBsAHkAIAB1AHMAZQBzACAAZABhAHQAYQAgAGYAbwByACAAMgAwADIAMAAtADIAMAAyADQALgAgAFUAcwBlACAAXAB1ADAAMAAyADcAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzAFwAdQAwADAAMgA3ACAAZABhAHQAYQAgAGYAbwByACAAXAB1ADAAMAAyADcATwB0AGgAZQByACAAagA9ADQAXAB1ADAAMAAyADcAIABjAGwAYQBzAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAEkAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMgAuADYAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdwBzAFwAIgAsADIALgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMgAuADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAcwBcACIALAAgADEALgA3ADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBcAG4ATgBXAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB3AGEAcwB0AGUAIAAoAE4AVwBqACkAIAAtACAAMgAwADIAMAAgAHQAbwAgADIAMAAyADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATwBuAGwAeQAgAHUAcwBlAHMAIABkAGEAdABhACAAZgBvAHIAIAAyADAAMgAwAC0AMgAwADIANAAuACAAVQBzAGUAIABcAHUAMAAwADIANwBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAXAB1ADAAMAAyADcAIABkAGEAdABhACAAZgBvAHIAIABcAHUAMAAwADIANwBPAHQAaABlAHIAIABqAD0ANABcAHUAMAAwADIANwAgAGMAbABhAHMAcwAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBXAGoAIABkAGEAaQBsAHkAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAHAAcgBvAHYAaQBkAGUAIABkAGEAaQBsAHkAIAB2AGEAbAB1AGUAIABmAG8AcgAgAE8AdABoAGUAcgBzACAAYwBsAGEAcwBzAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBDAGwAYQBzAHMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAYQBzAHMAXAAiACwAIABcACIATgBXAGoAXAAiACwAIABcACIATgBXAGoAIABkAGEAaQBsAHkAXAAiACwAIABcACIAQwBsAGEAcwBzACAAbgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGEAcgBzAFwAIgAsACAAMAAuADAANAA2ACwAIAAwAC4AMAA0ADYALAAgAFwAIgBCAG8AYQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB3AHMAXAAiACwAMAAuADAANAA5ACwAIAAwAC4AMAA0ADkALAAgAFwAIgBTAG8AdwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGkAbAB0AHMAXAAiACwAIAAwAC4AMAA0ADYALAAgADAALgAwADQANgAsACAAXAAiAEcAaQBsAHQAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByAHMAIAAoAGsAZwAvAGgAZQBhAGQALwB5AGUAYQByACkAXAAiACwAIAAxADEALgA0ACwAIAAwAC4AMAAzADEAMgAsACAAXAAiAE8AdABoAGUAcgBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXABuAEYAcgBhAGMARwBBAFMATQBtAFQAXABuACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcATgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgAyADoAIABTAHcAaQBuAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwBOACkAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVABcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByACAAKABEAHIAeQAgAGwAbwB0ACkAXAAiACwAIAAwAC4AMwAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADEAMgA1ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACAAKABVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AKQBcACIALAAgADAALgA1ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AGUAcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAIAAxACAAbQBvAG4AdABoACAAKABwAGkAdAAgAHMAdABvAHIAYQBnAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUAFwAbgBrAGcATgAyAE8AIAAtACAATgAgAC8AIABrAGcATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABiAHkAIABNAE0AUwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcATgAyAE8AIAAtACAATgAgAC8AIABrAGcATgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADMAOgAgAFMAdwBpAG4AZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABiAHkAIABNAE0AUwAgACgAawBnAE4AMgBPAC0ATgAvAGsAZwBOACkAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBtAFwAIgAsACAAXAAiAEUARgBtAFQAXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AG8AYwBrAHAAaQBsAGUAIAAoAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAbwByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABvAHIAdAAgAEgAUgBUACAAdABhAG4AawAgAHMAdABvAHIAYQBnAGUAIABcAHUAMAAwADMAYwAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMAAyACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQgAwAFwAbgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIABtAGUAdABoAGEAbgBlACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAoADIAMAAxADkAKQAsACAAQwBoAGEAcAB0AGUAcgAgADEAMAAgAFsANABdAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgA2AC4ANAA6ACAAUwB3AGkAbgBlACAALQAgAE0AQwBGAHMAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAAtACAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAEEAQwBUACwAIABzAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAxADAALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcAOAAsACAAMAAuADcAOAAsACAAMAAuADcANQAsACAAMAAuADcAMAAsACAAMAAuADcANAAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAZQByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAIAAxACAAbQBvAG4AdABoACAAKABwAGkAdAAgAHMAdABvAHIAYQBnAGUAKQBcACIALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFcAYwBvAFwAbgBrAGcAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAEEAdgBlAHIAYQBnAGUAIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABpAG4AdgBlAG4AdABvAHIAeQAgAGQAZQBmAGEAdQBsAHQAcwApACAAKABrAGcAKQAgACgAVwBjAG8AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA1ADoAIABTAHcAaQBuAGUAIAAtACAAQQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGkAbgB2AGUAbgB0AG8AcgB5ACAAZABlAGYAYQB1AGwAdABzACkAIAAoAGsAZwApACAAKABXAGMAbwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB3AHMAXAAiACwAIAAxADgAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAG8AYQByAHMAXAAiACwAIAAyADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGkAbAB0AHMAXAAiACwAIAAxADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAXAAiACwAIAAzADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzACAAYQB0ACAAdAB1AHIAbgBvAGYAZgBcACIALAAgADkANwBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXABuADQALgA1ACAAUwB3AGkAbgBlACAARgBpAGcAdQByAGUAIAA0AC4AOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1ACAAUwB3AGkAbgBlACAARgBpAGcAdQByAGUAIAA0AC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBuAHYAZQBuAHQAaQBvAG4AYQBsACAAaABvAHUAcwBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByACAAaABvAHUAcwBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAvAGYAcgBlAGUAIAByAGEAbgBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAbwByACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABlAHgAdAAgAHIAZQBmAGUAcgBzACAAdABvACAAXAB1ADAAMAAyADcAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAHUAMAAwADIANwAgAE0ATQBTACwAIABiAHUAdAAgAGUAcQB1AGEAdABpAG8AbgAgAHIAZQBmAGUAcgBzACAAdABvACAAXAB1ADAAMAAyADcAZAByAHkAbABvAHQAXAB1ADAAMAAyADcAIABNAE0AUwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXABuAEYAXABuAE0ASgAvAGsAZwAgAEMASAA0AFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAGcAYQBqAG8AdQBsAGUAcwAgAHAAZQByACAAawBpAGwAbwBnAHIAYQBtACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAALwAgAGsAZwAgAEMASAA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADUANQAuADIAMgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADUAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADUALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABzAHcAaQBuAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABEAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgACgAaABlAGEAZAApAFwAbgBNAF8AagAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAIAA9ACAAdABoAGUAIABhAHYAZQByAGEAZwBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAeQBzACAAbwBuACAAZgBhAHIAbQAgAGYAbwByACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE0AXwBqACwAIABEAF8AagAsAFwAbgAgACAAIAAgACgATgBfAGoAIAAqACAATQBfAGoAIAAqACAARABfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABzAHcAaQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABEAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABzAHcAaQBuAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgA1AC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgB0AGgAZQAgAGEAdgBlAHIAYQBnAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQB5AHMAIABvAG4AIABmAGEAcgBtACAAZgBvAHIAIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAG8AZgAgAHMAdwBpAG4AZQBcAG4ATQBfAGoAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagA9AFwAXABmAHIAYQBjAHsASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAOAAuADYAXABcAHQAaQBtAGUAcwAgADAALgAwADAANwB9AHsARgB9AFwAbgBJAF8AagAgAD0AIABkAGEAaQBsAHkAIABmAGUAZQBkACAAaQBuAGcAZQBzAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEYAIAA9ACAAbQBlAGcAYQBqAG8AdQBsAGUAcwAgAHAAZQByACAAawBpAGwAbwBnAHIAYQBtACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgATQBKAC8AawBnACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABGACwAXABuACAAIAAgACAAKABJAF8AagAgACoAIAAxADgALgA2ACAAKgAgADAALgAwADAANwApACAALwAgAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABvAGYAIABzAHcAaQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagA9AFwAXABmAHIAYQBjAHsASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAOAAuADYAXABcAHQAaQBtAGUAcwAgADAALgAwADAANwB9AHsARgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGYAZQBlAGQAIABpAG4AZwBlAHMAdABlAGQAIABiAHkAIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAOAAuADYAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIAAoAEcARQApACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAXAAiACwAIABcACIATQBKACAARwBFAC8AawBnACAAZgBlAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADAALgAwADAANwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABHAEUAIABpAG4AdABhAGsAZQAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAbQBlAHQAaABhAG4AZQAgAGIAeQAgAHMAdwBpAG4AZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAFwAIgAsACAAXAAiAG0AZQBnAGEAagBvAHUAbABlAHMAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIATQBKAC8AawBnACAAQwBIADQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAUICAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAbQBqAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ARABqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAIAA6ACAAZABhAHkAcwBcAG4ATQBtAGoAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABqACwAIABNAG0AagAsACAATgBqACwAXABuACAAIAAgACAARABqACAAKgAgAE0AbQBqACAAKgAgAE4AagAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAbQBqAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAagBcACIALABcACIAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAG8AZgAgAHMAdwBpAG4AZQBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBtAGoAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4ATQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdABoAGUAIABtAGEAbgB1AHIAZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXABuAE0AbQBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAbQBqAH0APQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQBNAF8AewBqAG0AVAB9AFwAbgBNAGoAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AagBtAFQALABcAG4AIAAgACAAIABTAFUATQAoAE0AagBtAFQAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AagBtAFQAMQAsACAATQBqAG0AVAAyACwAXABuACAAIAAgACAAIABTAFUATQAoAE0AagBtAFQAMQAsACAATQBqAG0AVAAyACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdABoAGUAIABtAGEAbgB1AHIAZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG0AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAbABhAHMAcwAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAAzACkAIABhAG4AZAAgACgANgApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAUwBwAGwAaQB0ACAAdgBhAHIAaQBhAGIAbABlACAATQBqAG0AIABpAG4AdABvACAATQBqAG0AVAAxACAAYQBuAGQAIABNAGoAbQBUADIAIABmAG8AcgAgAHMAdABhAGcAZQAgADEAIABhAG4AZAAgADIAIABNAE0AUwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBpAGoAbQBUADEAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBpAGoAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEYAVgBTAGoAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAE0AQwBGAGkAbQAsACAAQgBPACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAFYAUwBqACAAKgAgAEYAVgBTAGoAbQBUADEAIAAqACAATQBDAEYAaQBtACAAKgAgAEIATwAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBpAGoAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMQAgACgANAApACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXABuAEYAVgBTAGoAbQBUADEAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMAUwBfAHsAbQB9ACkAXABuAE0ATQBTAGoAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAcAByAGkAbwByACAAdABvACAAcwBvAGwAaQBkACAAcwBlAHAAYQByAGEAdABpAG8AbgAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFMAUwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAagBtAFQAMQAsACAAUwBTAG0ALABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABTAFMAbQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBTAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABwAHIAaQBvAHIAIAB0AG8AIABzAG8AbABpAGQAIABzAGUAcABhAHIAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAUwBtAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBWAFMAagBtADQAVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQB9ACkAXABuAE0ATQBTAGoAbQA0AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAE0AUwBqAG0AMQA3ADkAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBqAG0ANABUADEALAAgAE0ATQBTAGoAbQAxADcAOQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATQBNAFMAagBtADQAVAAxACAAKwAgACgATQBNAFMAagBtADEANwA5AFQAMQAgACoAIABTAFMAbQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAXABuACAAIAAgACAATQBNAFMAagBtAFQAMQBfADEALAAgAE0ATQBTAGoAbQBUADEAXwAyACwAIABNAE0AUwBqAG0AVAAxAF8AMwAsACAATQBNAFMAagBtAFQAMQBfADQALAAgAE0ATQBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAAUwBTAGoAbQBUADEAXwAxACwAIABTAFMAagBtAFQAMQBfADIALAAgAFMAUwBqAG0AVAAxAF8AMwAsACAAUwBTAGoAbQBUADEAXwA0ACwAIABTAFMAagBtAFQAMQBfADUALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADQAVAAxACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAxACAAKgAgAFMAUwBqAG0AVAAxAF8AMQApACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAyACAAKgAgAFMAUwBqAG0AVAAxAF8AMgApACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAzACAAKgAgAFMAUwBqAG0AVAAxAF8AMwApACAAKwBcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8ANAAgACoAIABTAFMAagBtAFQAMQBfADQAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADUAIAAqACAAUwBTAGoAbQBUADEAXwA1ACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAagBtADQAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADEALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADcALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA3ACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AOQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtADQAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtADEANwA5AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABNAE0AUwAgADEALAAgADcALAAgAGEAbgBkACAAOQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAbQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAUwBwAGwAaQB0ACAAZQBxAHUAYQB0AGkAbwBuACAAZgBvAHIAIABNAE0AUwBtAD0AMQAsADcALAA5ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAGkAdABlAG0AcwAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAFwAIgApADsAXABuACAAIABcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBpAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBUAGoAbQBUADIAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4AaQAgAD0AIABzAHQAYQB0AGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAVABqAG0AVAAyACwAIABCAE8ALAAgAE0ATQBTAGoAbQBUADIALAAgAE0AQwBGAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABWAFMAVABqAG0AVAAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABWAFMAVABqAG0AVAAyACkALAAgAFYAUwBUAGoAbQBUADIALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0AVAAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAyACkALAAgAE0ATQBTAGoAbQBUADIALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAVABqAG0AVAAyACAAKgAgAEIATwAgACoAIABNAE0AUwBqAG0AVAAyACAAKgAgAE0AQwBGAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABlAGEAYwBoACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAFQAagBtAFQAMgBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAA3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAFQAagBtAFQAMgBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAA3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAVABcACIALABcACIATQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiALAAQwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBWAFMAVABpAGoAbQBUADIAXABuAGsAZwAgAFYAUwBcAG4AVgBTAFQAXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFYAUwBMAF8AewBtACwAVAA9ADEAfQApAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBGAFYAUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBMAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagAsACAARgBWAFMAagBtAFQAMQAsACAAVgBTAEwAbQBUADEALABcAG4AIAAgACAAIABWAFMAagAgACoAIABGAFYAUwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABWAFMATABtAFQAMQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAVABpAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFYAUwBMAF8AewBtACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAVgBTAGoAbQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAxACAAKAA0ACkAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADMAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABEAGkAcgBlAGMAdAAgAE4AMgBPACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXABuAEUAXwBOADIATwBkAGkAcgBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgACgAawBnACAATgApAFwAbgBFAEYAXwBqAG0AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBOAF8AagBtAFQAIAAqACAARQBGAF8AagBtACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADIAKQAoADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBtAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQBUADEAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AGoAbQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgACgAawBnACAATgApAFwAbgBGAE4AXwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABzAHkAcwB0AGUAbQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABGAE4AXwBqAG0AVAAxACwAXABuACAAIAAgACAAQQBFAF8AagAgACoAIABGAE4AXwBqAG0AVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtAFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0ALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAagBtACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALAAgAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAGoAbQBUADEAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADMAIAAoADMAKQAoADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAbgBGAE4AXwBqAG0AVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYATgBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBOAF8AewBtAH0AKQBcAG4ATQBNAFMAXwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgBTAE4AXwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAGoAbQBUADEALAAgAFMATgBfAG0ALABcAG4AIAAgACAAIABNAE0AUwBfAGoAbQBUADEAIAAqACAAKAAxACAALQAgAFMATgBfAG0AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgACgAZQB4AGMAbAB1AGQAaQBuAGcAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AagBtAFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AewBqAG0ALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBTAE4AXwB7AG0AfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0AVAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMATgBfAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAE4AXwBqAG0ANABUADEAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ARgBOAF8AewBqAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMATgBfAHsAbQB9ACkAXABuAE0ATQBTAF8AagBtADQAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAE0ATQBTAFwAbgBNAE0AUwBfAGoAbQAxADcAOQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAbABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzACAAKABtAD0AMQAsADcALAA5ACkAXABuAFMATgBfAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAGoAbQA0AFQAMQAsACAATQBNAFMAXwBqAG0AMQA3ADkAVAAxACwAIABTAE4AXwBtACwAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEAIAArACAAKABNAE0AUwBfAGoAbQAxADcAOQBUADEAIAAqACAAUwBOAF8AbQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAGoAbQA0AFQAMQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAATQBNAFMAagBtAFQAMQBfADMALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAUwBTAGoAbQBUADEAXwAyACwAIABTAFMAagBtAFQAMQBfADMALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAUwBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAATQBNAFMAXwBqAG0ANABUADEAIAArACAAKABNAE0AUwBqAG0AVAAxAF8AMQAgACoAIABTAFMAagBtAFQAMQBfADEAKQAgACsAIAAoAE0ATQBTAGoAbQBUADEAXwAyACAAKgAgAFMAUwBqAG0AVAAxAF8AMgApACAAKwAgACgATQBNAFMAagBtAFQAMQBfADMAIAAqACAAUwBTAGoAbQBUADEAXwAzACkAIAArACAAKABNAE0AUwBqAG0AVAAxAF8ANAAgACoAIABTAFMAagBtAFQAMQBfADQAKQAgACsAIAAoAE0ATQBTAGoAbQBUADEAXwA1ACAAKgAgAFMAUwBqAG0AVAAxAF8ANQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AagBtADQAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBOAF8AewBqAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMATgBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAE4AXwB7AGoAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AMQAsAFQAPQAxAH0AKQArACgATQBNAFMAXwB7AGoALABtAD0ANwAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADcALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA5ACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADQAVAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADEANwA5AFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABsAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAIAAoAG0APQAxACwANwAsADkAKQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAE4AXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFMAcABsAGkAdAAgAGUAcQB1AGEAdABpAG8AbgAgAGYAbwByACAATQBNAFMAbQA9ADEALAA3ACwAOQAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABpAHQAZQBtAHMAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAHMAdwBpAG4AZQAgAGcAcgBvAHUAcABcAG4AQQBFAF8AagBcAG4AawBnACAATgBcAG4AQQBFAF8AewBqAH0APQBOAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE4AVwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgACgAaABlAGEAZAApAFwAbgBOAFcAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAcgBvAGQAdQBjAGUAZAAgAGkAbgAgAHMAdwBpAG4AZQAgAG0AYQBuAHUAcgBlACAAYQBuAGQAIAB3AGEAcwB0AGUAIABmAGUAZQBkACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgACgAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBEAF8AagAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAcwB3AGkAbgBlACAAZwByAG8AdQBwACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBXAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAFcAXwBqACAAKgAgAEQAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAGYAcgBvAG0AIABlAGEAYwBoACAAcwB3AGkAbgBlACAAZwByAG8AdQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAFcAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBXAF8AagBcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAHIAbwBkAHUAYwBlAGQAIABpAG4AIABzAHcAaQBuAGUAIABtAGEAbgB1AHIAZQAgAGEAbgBkACAAdwBhAHMAdABlACAAZgBlAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAXAAiACwAIABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABzAHcAaQBuAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AVAAyAFwAbgBrAGcAIABOAFwAbgBNAE4AXwB7AGoAbQAsAFQAPQAyAH0APQBOAFQAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAbgBOAFQAXwBqAG0AVAAyACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgACgAawBnACAATgApAFwAbgBNAE0AUwBfAGoAbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACwAIABNAE0AUwBfAGoAbQBUADIALABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACAAKgAgAE0ATQBTAF8AagBtAFQAMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABfAGoAbQBUADIAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAA3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATgBUAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATgBUAF8AewBqAG0ALABUAD0AMgB9AD0ATQBOAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtACwAVAA9ADEAfQAtAEUARgBfAHsAbQAsAFQAPQAxAH0AKQBcAG4ATQBOAF8AagBtAFQAMQAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTACAAKABrAGcAIABOACkAXABuAEYAcgBhAGMARwBBAFMATQBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABhAHQAIABzAHQAYQBnAGUAIAAxAFwAbgBFAEYAXwBtAFQAMQAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABhAHQAIABzAHQAYQBnAGUAIAAxAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAxACwAIABGAHIAYQBjAEcAQQBTAE0AbQBUADEALAAgAEUARgBfAG0AVAAxACwAXABuACAAIAAgACAATQBOAF8AagBtAFQAMQAgACoAIAAoADEAIAAtACAARgByAGEAYwBHAEEAUwBNAG0AVAAxACAALQAgAEUARgBfAG0AVAAxACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQBNAE4AXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0ALABUAD0AMQB9AC0ARQBGAF8AewBtACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMQBcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAHMAdwBpAG4AZQAgAGMAbABhAHMAcwAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAyACkAKAA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAMQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABhAHQAIABzAHQAYQBnAGUAIAAxAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADEAXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAYQB0ACAAcwB0AGEAZwBlACAAMQBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBcAG4AQQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBNAFMAXABuAEUAXwBOADIATwBNAE0AUwBhAGQAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABhAGQAfQA9AE0ATQBTAF8AewBBAFQATQBPAFMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAE0AUwBfAEEAVABNAE8AUwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgACgAawBnACAATgApAFwAbgBFAEYAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBNAFMAXwBBAFQATQBPAFMAIAAqACAARQBGAF8ATgAyAE8AIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8ATQBNAFMAYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADUAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALAAgAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBcAG4AVABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAbgBNAE0AUwBfAEEAVABNAE8AUwBcAG4AawBnACAATgBcAG4ATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIAAoACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABGAHIAYQBjAEcAQQBTAE0AbQBUACwAXABuACAAIAAgACAATQBOAF8AagBtAFQAIAAqACAARgByAGEAYwBHAEEAUwBNAG0AVABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgAMgApACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgA3ACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATABlAGEAYwBoAGkAbgBnACAAQQBuAGQAIABSAHUAbgBvAGYAZgAgAE4AMgBPACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXABuAEEAbgBuAHUAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABlAGEAYwBoACAATQBNAFMAXABuAEUAXwBOADIATwBsAGUAYQBjAGgAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0ATgBMAGUAYQBjAGgAXwB7AGoAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBOAEwAZQBhAGMAaABfAGoAbQA1ACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AbABlAGEAYwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4AVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARAB1AGUAIAB0AG8AIABzAHQAcgBpAGMAdAAgAGUAbgB2AGkAcgBvAG4AbQBlAG4AdABhAGwAIABjAG8AbgB0AHIAbwBsAHMALAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAYQByAGUAIABlAHMAdABpAG0AYQB0AGUAZAAgAG8AbgBsAHkAIABmAG8AcgAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAAoAG0APQA1ACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4ATABlAGEAYwBoAF8AagBtADUALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBOAEwAZQBhAGMAaABfAGoAbQA1ACAAKgAgAEUARgBfAGwAZQBhAGMAaAAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAG4AbgB1AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZQBhAGMAaAAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADcALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGwAZQBhAGMAaAB9AD0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4ATABlAGEAYwBoAF8AagBtADUAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4ANwAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQBcAG4AawBnACAATgBcAG4ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9AD0ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAEUAVABcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXwB7AE0AUwB9AFwAbgBNAE4AXwBqAG0ANQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAZAByAHkAbABvAHQAIABNAE0AUwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAFcARQBUACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQA1AFQAMQAsACAARgByAGEAYwBXAEUAVAAsACAARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMALABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEAIAAqACAARgByAGEAYwBXAEUAVAAgACoAIABGAHIAYQBjAEwARQBBAEMASABfAE0AUwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4ATABlAGEAYwBoAF8AagBtADUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADcALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9AD0ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAEUAVABcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXwB7AE0AUwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQA1AFQAMQBcACIALAAgAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQA6ACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANQAuADEALgA5ACAATQBhAG4AdQByAGUAIABBAHAAcABsAGkAZQBkACAAdABvACAAUwBvAGkAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAgAFAARgBcAG4ATQBOAF8AagBtAFQAMgAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcABpAGcAZwBlAHIAeQAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAsACAARQBGAF8AbQBUADIALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyACwAIABNAE4ATABlAGEAYwBoAF8AagBtADUALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAKQAgAC0AIABNAE4ATABlAGEAYwBoAF8AagBtADUAKQAgACoAIABQAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AKABNAE4AXwB7AGoAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIAfQApAC0ATQBOAEwAZQBhAGMAaABfAHsAagBtAD0ANQB9ACkAXABcAHQAaQBtAGUAcwAgAFAARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4AMwAgACgANgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAEwAZQBhAGMAaABfAGoAbQA1AFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA1AC4AMQAuADcAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABGAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHAAaQBnAGcAZQByAHkAIABiAG8AdQBuAGQAYQByAHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQAoAE0ATgBfAHsAagBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgB9ACkALQBNAE4ATABlAGEAYwBoAF8AewBqAG0APQA1AH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAbgBNAE4AXwBqAG0AVAAyACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIABhAHQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ATQBOAEwAZQBhAGMAaABfAGoAbQA1ACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABrAGcAIABOAFwAbgBQAEYAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABwAGkAZwBnAGUAcgB5ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAyACwAIABFAEYAXwBtAFQAMgAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIALAAgAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyACAAKgAgACgAMQAgAC0AIABFAEYAXwBtAFQAMgAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgApACAALQAgAE0ATgBMAGUAYQBjAGgAXwBqAG0ANQApACAAKgAgACgAMQAgAC0AIABQAEYAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgA5ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQAoAE0ATgBfAHsAagBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgB9ACkALQBNAE4ATABlAGEAYwBoAF8AewBqAG0APQA1AH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVAAyAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAE0ATQBTACAAYQB0ACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANQAuADEALgAzACAAKAA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAyAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGEAdAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4ATABlAGEAYwBoAF8AagBtADUAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADUALgAxAC4ANwAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcABpAGcAZwBlAHIAeQAgAGIAbwB1AG4AZABhAHIAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgBlAGUAZABJAG4AdABhAGsAZQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AVwBhAHMAdABlAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAFcAYQBzAHQAZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAGcAZQBuAEkAbgBXAGEAcwB0AGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMAdABpAG8AbgBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwB0AGkAbwBuAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAHQAaQBvAG4ATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARAByAHkAbABvAHQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAHIAeQBsAG8AdABNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAcgB5AGwAbwB0AE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQBnAGEAagBvAHUAbABlAHMAUABlAHIASwBpAGwAbwBnAHIAYQBtAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAGcAYQBqAG8AdQBsAGUAcwBQAGUAcgBLAGkAbABvAGcAcgBhAG0ATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAZwBhAGoAbwB1AGwAZQBzAFAAZQByAEsAaQBsAG8AZwByAGEAbQBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8AUwB3AGkAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBTAHcAaQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA1AF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAFMAdwBpAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADUAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADMAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUAByAGkAbQBhAHIAeQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8AMwBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAHIAaQBtAGEAcgB5AE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwAzAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAcgBpAG0AYQByAHkATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA1AF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANQBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADUAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMQBfAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADEAXwBBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAxAF8AQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA1AF8AXwAyAF8AVABvAHQAYQBsAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANQBfAF8AMgBfAFQAbwB0AGEAbABOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADUAXwBfADIAXwBUAG8AdABhAGwATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADEAXwBBAG4AbgB1AGEAbABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMQBfAEEAbgBuAHUAYQBsAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAxAF8AQQBuAG4AdQBhAGwARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARgByAG8AbQBEAHIAeQBsAG8AdABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEYAcgBvAG0ARAByAHkAbABvAHQATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBGAHIAbwBtAEQAcgB5AGwAbwB0AE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8AUwB3AGkAbgBlAF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBTAHcAaQBuAGUAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAFMAdwBpAG4AZQBfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
